--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1317,67 +1317,67 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1435,27 +1435,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校（RCA 优先）</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
@@ -1473,37 +1473,37 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1513,27 +1513,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
+          <t>同步发伦敦6校（RCA 优先）</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
@@ -1551,37 +1551,37 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>同步发 UK Food Lovers</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
@@ -1629,17 +1629,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1669,27 +1669,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>同步发 Harper Adams、Wolverhampton</t>
+          <t>同步发格拉斯哥3校</t>
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
@@ -1707,67 +1707,67 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发格拉斯哥3校</t>
         </is>
       </c>
       <c r="N17" s="2" t="n"/>
@@ -1785,17 +1785,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1805,47 +1805,47 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发伯明翰3校</t>
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
@@ -1863,17 +1863,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1903,27 +1903,27 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>RCA 优先推</t>
+          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
@@ -1941,37 +1941,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1981,27 +1981,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 UK Food Lovers</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -2019,67 +2019,67 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>同步发 Harper Adams、Wolverhampton</t>
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
@@ -2102,62 +2102,62 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>The Gaming Corner</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>第6名</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>免费</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
@@ -2175,17 +2175,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2215,22 +2215,22 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2253,32 +2253,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -2331,17 +2331,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2371,22 +2371,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2409,17 +2409,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2429,47 +2429,47 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>⚠️日期待核实</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
@@ -2487,17 +2487,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
@@ -2565,62 +2565,62 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2643,57 +2643,57 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2721,62 +2721,62 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2799,62 +2799,62 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2877,17 +2877,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Richmond Family Fireworks</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2897,47 +2897,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -2955,62 +2955,62 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3033,62 +3033,62 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3103,6 +3103,1098 @@
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>30 Oct 2026（周五）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Harper Adams Campus Life</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花) + 一日游</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Wolverhampton Freshers Hub 2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花) + 一日游</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>University of Lancaster</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>运动户外(游泳)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Swim Wave Tribe</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>The University of Manchester</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Islington Mill, James Street, Salford</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体 + 社交类(女性)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Corner; Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>The University of Manchester</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Manchester 多个场地</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>社交类(女性) + 兴趣类(手工)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Corner</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>The University of Manchester</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Manchester（场地待公布）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>27 Oct 2026（周二）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>社交类(女性交友)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Corner</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/金属)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>13–14 Nov 2026</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/节庆)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh（多个场地）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>同步发爱丁堡2校</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -3394,11 +4486,11 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>只有烟花节里的 DJ 场，还没专门搜演出</t>
+          <t>都来自城市轮顺带（烟花节 DJ、Skindred 巡演、格拉斯哥音乐节）；还没专门做全国演出轮</t>
         </is>
       </c>
     </row>
@@ -3415,17 +4507,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>顺带匹配（没专门搜）</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>计划：第12轮起按兴趣分批</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3494,7 +4582,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
     </row>
@@ -3778,15 +4866,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第4轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>计划：第4轮 格拉斯哥+爱丁堡</t>
+          <t>格拉斯哥同城共用；Glasgow Green 烟花没收录：搜到的"Mon 5 Nov"是 2018 年的旧页面，而且当地媒体说篝火夜活动已暂停</t>
         </is>
       </c>
     </row>
@@ -3828,15 +4916,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第4轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>计划：第4轮 格拉斯哥+爱丁堡</t>
+          <t>格拉斯哥同城共用；Glasgow Green 烟花没收录：搜到的"Mon 5 Nov"是 2018 年的旧页面，而且当地媒体说篝火夜活动已暂停</t>
         </is>
       </c>
     </row>
@@ -3853,15 +4941,15 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第4轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>计划：第4轮 格拉斯哥+爱丁堡</t>
+          <t>爱丁堡同城共用；Samhuinn 火节（10/31）已售罄没收录；Meadowbank 烟花 2017 年起就停办了；Skerryvore 演出票价从 £115 起，太贵，没收录</t>
         </is>
       </c>
     </row>
@@ -3957,11 +5045,11 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>伯明翰同城共用；未达 3–5 条：BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
+          <t>伯明翰同城共用；第4轮顺带补了 Skindred 伯明翰站；BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
         </is>
       </c>
     </row>
@@ -3982,11 +5070,11 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>伯明翰同城共用；未达 3–5 条：BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
+          <t>伯明翰同城共用；第4轮顺带补了 Skindred 伯明翰站；BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
         </is>
       </c>
     </row>
@@ -4270,15 +5358,15 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第4轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>计划：第4轮 格拉斯哥+爱丁堡</t>
+          <t>格拉斯哥同城共用；Glasgow Green 烟花没收录：搜到的"Mon 5 Nov"是 2018 年的旧页面，而且当地媒体说篝火夜活动已暂停</t>
         </is>
       </c>
     </row>
@@ -4645,11 +5733,11 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>伯明翰同城共用；未达 3–5 条：BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
+          <t>伯明翰同城共用；第4轮顺带补了 Skindred 伯明翰站；BCLM 万圣节夜日期对不上（搜到的是 2021 年页面），Moseley 烟花已售罄</t>
         </is>
       </c>
     </row>
@@ -4716,15 +5804,15 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第4轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>计划：第4轮 格拉斯哥+爱丁堡</t>
+          <t>爱丁堡同城共用；Samhuinn 火节（10/31）已售罄没收录；Meadowbank 烟花 2017 年起就停办了；Skerryvore 演出票价从 £115 起，太贵，没收录</t>
         </is>
       </c>
     </row>
@@ -4764,7 +5852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4918,10 +6006,58 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>没收录（售罄）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Samhuinn Fire Festival（爱丁堡 Calton Hill，10/31）：官方票务页显示已售罄，只能排候补</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>日期对不上→没收录</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow Green 烟花：搜到的"Mon 5 Nov"是 2018 年的旧页面，而且当地媒体说篝火夜活动已暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>日期待核实</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GlasGLOW：起始日有 16 Oct 和 24 Oct 两种说法，表里已标出来</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>票价偏高→没收录</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Skerryvore @ Edinburgh Corn Exchange（11/6）：Ticketmaster 显示从 £115 起</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1634,52 +1634,52 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>同步发格拉斯哥3校</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1790,32 +1790,32 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>同步发伯明翰3校</t>
+          <t>同步发格拉斯哥3校</t>
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
@@ -1863,67 +1863,67 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
+          <t>同步发伯明翰3校</t>
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
@@ -1941,67 +1941,67 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第8名</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>同步发 UK Food Lovers</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -2019,17 +2019,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2039,37 +2039,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
+          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>同步发 Harper Adams、Wolverhampton</t>
+          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
@@ -2097,37 +2097,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 UK Food Lovers</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
@@ -2175,67 +2175,67 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Harper Adams、Wolverhampton</t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
@@ -2258,62 +2258,62 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>The Gaming Corner</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2371,22 +2371,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2414,32 +2414,32 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2449,27 +2449,27 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
@@ -2492,62 +2492,62 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>第6名</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>免费</t>
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
@@ -2643,32 +2643,32 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2683,27 +2683,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
@@ -2721,17 +2721,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2761,22 +2761,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2819,17 +2819,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2839,22 +2839,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2912,32 +2912,32 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>⚠️日期待核实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -2955,37 +2955,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2995,22 +2995,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3033,32 +3033,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Richmond Family Fireworks</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3068,32 +3068,32 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N34" s="2" t="n"/>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3189,17 +3189,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3229,22 +3229,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3267,37 +3267,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3307,22 +3307,22 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3365,37 +3365,37 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3423,37 +3423,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3501,37 +3501,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>运动户外(游泳)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Swim Wave Tribe</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3584,57 +3584,57 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Girls' Corner; Reel Talk Club</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3657,62 +3657,62 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Manchester 多个场地</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
+          <t>社交类(女性) + 兴趣类(手工)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3735,62 +3735,62 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Manchester（场地待公布）</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>27 Oct 2026（周二）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>社交类(女性交友)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3818,57 +3818,57 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3891,17 +3891,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh's Christmas 2026（开幕）</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3911,42 +3911,42 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/节庆)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3969,37 +3969,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4009,22 +4009,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4052,57 +4052,57 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4125,39 +4125,39 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>Page Turners Club</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>21–31 Oct 2026</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>兴趣类(文学/讲故事)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>中热度</t>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N48" s="2" t="n"/>
@@ -4195,6 +4195,630 @@
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh（多个场地）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>同步发爱丁堡2校</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Club/电子)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Durham university</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>同步发 Durham university</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/赛马)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Reverend and The Makers 演唱会</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>14 Nov 2026（周六）19:00 开门</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Northumbria 优先</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Durham university</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Durham university</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Durham Jazz Festival 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>23–25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/爵士)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -4486,7 +5110,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -5408,15 +6032,15 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第5轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>计划：第5轮 纽卡斯尔+杜伦</t>
+          <t>纽卡斯尔同城共用，两个群内容完全一样；圣诞市集 11/19 才开，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -5433,15 +6057,15 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第5轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>计划：第5轮 纽卡斯尔+杜伦</t>
+          <t>纽卡斯尔同城共用，两个群内容完全一样；圣诞市集 11/19 才开，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -5458,15 +6082,15 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第5轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>计划：第5轮 纽卡斯尔+杜伦</t>
+          <t>纽卡斯尔同城共用，两个群内容完全一样；圣诞市集 11/19 才开，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -5483,15 +6107,15 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第5轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>计划：第5轮 纽卡斯尔+杜伦</t>
+          <t>未达 3–5 条：Lumiere 灯光节 2025 年已停办；Durham Book Festival 在 10/9–11，不在窗口内；Hardwick Hall 烟花的 2026 年日期没确认</t>
         </is>
       </c>
     </row>
@@ -5852,7 +6476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6054,10 +6678,46 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>已停办</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Durham Lumiere 灯光节：2025 年是最后一届，2026 年没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>日期对不上→没收录</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Hardwick Hall 烟花（Sedgefield）：搜到的"Sat 5 / Sun 6 Nov"是 2022 年的日期，2026 年日期没确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>日期待核实</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Beamish 万圣节夜场：官网确认有 28 Oct 那一场，整季场次各来源说法不一</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1244,52 +1244,52 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Leeds International Film Festival（第 40 届）</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; The University of Manchester</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>同步发 Girls' Corner</t>
+          <t>同步发利兹2群</t>
         </is>
       </c>
       <c r="N11" s="2" t="n"/>
@@ -1322,52 +1322,52 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>Girls' Corner; The University of Manchester</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>同步发 Girls' Corner</t>
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
@@ -1395,67 +1395,67 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1513,27 +1513,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校（RCA 优先）</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校</t>
+          <t>同步发伦敦6校（RCA 优先）</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1669,27 +1669,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>同步发纽卡斯尔3群</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>同步发格拉斯哥3校</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N17" s="2" t="n"/>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1825,22 +1825,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1903,27 +1903,27 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>同步发伯明翰3校</t>
+          <t>同步发格拉斯哥3校</t>
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1981,27 +1981,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>第8名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>同步发纽卡斯尔3群</t>
+          <t>同步发伯明翰3校</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -2019,67 +2019,67 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第8名</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
@@ -2097,67 +2097,67 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第9名</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>同步发 UK Food Lovers</t>
+          <t>同步发利兹2群</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
@@ -2175,17 +2175,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2195,37 +2195,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
+          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>同步发 Harper Adams、Wolverhampton</t>
+          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
@@ -2253,37 +2253,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2293,17 +2293,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 UK Food Lovers</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -2331,67 +2331,67 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Harper Adams、Wolverhampton</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -2414,62 +2414,62 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>The Gaming Corner</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
@@ -2648,62 +2648,62 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>第6名</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>免费</t>
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2761,27 +2761,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
@@ -2799,32 +2799,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
@@ -2877,17 +2877,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2917,22 +2917,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2995,22 +2995,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3068,32 +3068,32 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>⚠️日期待核实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="n"/>
@@ -3111,37 +3111,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3189,32 +3189,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Richmond Family Fireworks</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3224,32 +3224,32 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N36" s="2" t="n"/>
@@ -3272,57 +3272,57 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3385,22 +3385,22 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3423,37 +3423,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3463,22 +3463,22 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3501,17 +3501,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3521,37 +3521,37 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3579,37 +3579,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3657,37 +3657,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>运动户外(游泳)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Swim Wave Tribe</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3740,57 +3740,57 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Girls' Corner; Reel Talk Club</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3813,62 +3813,62 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Manchester 多个场地</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
+          <t>社交类(女性) + 兴趣类(手工)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3891,62 +3891,62 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Manchester（场地待公布）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>27 Oct 2026（周二）</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>社交类(女性交友)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3974,57 +3974,57 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4047,17 +4047,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh's Christmas 2026（开幕）</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4067,42 +4067,42 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/节庆)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4125,37 +4125,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4208,57 +4208,57 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4281,39 +4281,39 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
           <t>Page Turners Club</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>21–31 Oct 2026</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>兴趣类(文学/讲故事)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
-        </is>
-      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>中热度</t>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="2" t="n"/>
@@ -4359,62 +4359,62 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4437,17 +4437,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4457,47 +4457,47 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>同步发 Durham university</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N52" s="2" t="n"/>
@@ -4515,37 +4515,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛马)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4555,27 +4555,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发谢菲尔德2校</t>
         </is>
       </c>
       <c r="N53" s="2" t="n"/>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4628,32 +4628,32 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Northumbria 优先</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N54" s="2" t="n"/>
@@ -4671,39 +4671,39 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
           <t>Durham university</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
-        </is>
-      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>高热度</t>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Durham university</t>
         </is>
       </c>
       <c r="N55" s="2" t="n"/>
@@ -4749,62 +4749,62 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Durham Jazz Festival 2026</t>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/爵士)</t>
+          <t>年轻人娱乐(烟花/赛马)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4819,6 +4819,864 @@
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Reverend and The Makers 演唱会</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>14 Nov 2026（周六）19:00 开门</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Northumbria 优先</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Durham university</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Durham university</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Durham Jazz Festival 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>23–25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/爵士)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(灯光艺术节)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Leeds International Film Festival（第 40 届）</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>13 Nov 2026（周五）19:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Off the Shelf Festival of Words 2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Sheffield（市内多个场地）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲座)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>5 Nov 2026（周四）16:00–21:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Club/学生夜)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Study Break Crew</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>UoS 优先；⚠️日期待核实</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield Uni Student Hub</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）17:00 开门</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>成人 £5，很便宜，离市中心近</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield Uni Student Hub</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/音乐)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -5110,7 +5968,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -5135,7 +5993,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
     </row>
@@ -5206,7 +6064,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
     </row>
@@ -5761,15 +6619,15 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第6轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>计划：第6轮 利兹+谢菲尔德+哈德斯菲尔德</t>
+          <t>谢菲尔德同城共用；DocFest 在 6 月，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -5786,15 +6644,15 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第6轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>计划：第6轮 利兹+谢菲尔德+哈德斯菲尔德</t>
+          <t>谢菲尔德同城共用；DocFest 在 6 月，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -6157,15 +7015,15 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第6轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>计划：第6轮 利兹+谢菲尔德+哈德斯菲尔德</t>
+          <t>利兹同城共用，两个群内容完全一样；Roundhay Park 等 6 个市政篝火已被市议会决定停办</t>
         </is>
       </c>
     </row>
@@ -6182,15 +7040,15 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第6轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>计划：第6轮 利兹+谢菲尔德+哈德斯菲尔德</t>
+          <t>利兹同城共用，两个群内容完全一样；Roundhay Park 等 6 个市政篝火已被市议会决定停办</t>
         </is>
       </c>
     </row>
@@ -6207,15 +7065,15 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第6轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>计划：第6轮 利兹+谢菲尔德+哈德斯菲尔德</t>
+          <t>未达 3–5 条：hcmf// 当代音乐节在 11/20–29，不在窗口内；学生会官网只能看到 9 月的活动</t>
         </is>
       </c>
     </row>
@@ -6476,7 +7334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6714,10 +7572,46 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>已停办</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Leeds Roundhay Park 等 6 个市政篝火：市议会已决定停办（Leeds Castle 烟花在肯特郡，跟利兹无关，没收录）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>日期待核实</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Leadmill Fridays 万圣节特别场：活动页没写年份，推定 30 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>日期冲突</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>LIFF：有来源写 5–22 Nov，主流来源写 29 Oct–15 Nov；两种说法都在窗口内</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2253,17 +2253,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>同步发 UK Food Lovers</t>
+          <t>同步发 The University of Manchester</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -2331,17 +2331,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies</t>
+          <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2351,37 +2351,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
+          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>同步发 Harper Adams、Wolverhampton</t>
+          <t>同步发 UK Food Lovers</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -2409,57 +2409,57 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Harper Adams、Wolverhampton</t>
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>The Gaming Corner</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2570,62 +2570,62 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
@@ -2648,32 +2648,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2683,27 +2683,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2761,27 +2761,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
@@ -2882,32 +2882,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2917,27 +2917,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -2955,17 +2955,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2995,22 +2995,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3073,22 +3073,22 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3209,47 +3209,47 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>第4名</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N36" s="2" t="n"/>
@@ -3267,67 +3267,67 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Richmond Family Fireworks</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N37" s="2" t="n"/>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3365,42 +3365,42 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3463,22 +3463,22 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3501,37 +3501,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3677,37 +3677,37 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3735,37 +3735,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Lancaster city centre（历史建筑和街区）</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3813,37 +3813,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>运动户外(游泳)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Swim Wave Tribe</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3896,62 +3896,62 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Platt Fields 就在 Fallowfield</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
@@ -3969,17 +3969,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3989,17 +3989,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>31 Oct 2026（周六）20:00–04:00</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
+          <t>年轻人娱乐(Club/House)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4009,22 +4009,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4047,17 +4047,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4067,42 +4067,42 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4125,37 +4125,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Girls' Corner; Reel Talk Club</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4203,62 +4203,62 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh's Christmas 2026（开幕）</t>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+          <t>Manchester 多个场地</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/节庆)</t>
+          <t>社交类(女性) + 兴趣类(手工)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4281,62 +4281,62 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>Manchester（场地待公布）</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>27 Oct 2026（周二）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>社交类(女性交友)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4359,62 +4359,62 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4477,27 +4477,27 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="2" t="n"/>
@@ -4515,37 +4515,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4555,27 +4555,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>同步发谢菲尔德2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N53" s="2" t="n"/>
@@ -4593,37 +4593,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4633,17 +4633,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4671,17 +4671,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4691,37 +4691,37 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>同步发 Durham university</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="n"/>
@@ -4749,57 +4749,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛马)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -4827,17 +4827,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4847,17 +4847,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4867,27 +4867,27 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Northumbria 优先</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N57" s="2" t="n"/>
@@ -4905,67 +4905,67 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发谢菲尔德2校</t>
         </is>
       </c>
       <c r="N58" s="2" t="n"/>
@@ -4983,32 +4983,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Durham Jazz Festival 2026</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/爵士)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5018,27 +5018,27 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5061,37 +5061,37 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(灯光艺术节)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5101,27 +5101,27 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Durham university</t>
         </is>
       </c>
       <c r="N60" s="2" t="n"/>
@@ -5139,62 +5139,62 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Leeds International Film Festival（第 40 届）</t>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>年轻人娱乐(烟花/赛马)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5217,17 +5217,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>13 Nov 2026（周五）19:00</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -5257,27 +5257,27 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Northumbria 优先</t>
         </is>
       </c>
       <c r="N62" s="2" t="n"/>
@@ -5295,57 +5295,57 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5373,57 +5373,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+          <t>Durham Jazz Festival 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026（周四）16:00–21:00</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(Live Music/爵士)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5451,67 +5451,67 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
+          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
+          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
+          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/学生夜)</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Study Break Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
+          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
+          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
+          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>UoS 优先；⚠️日期待核实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N65" s="2" t="n"/>
@@ -5529,17 +5529,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield Uni Student Hub</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
+          <t>Leeds International Film Festival（第 40 届）</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -5549,42 +5549,42 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）17:00 开门</t>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>成人 £5，很便宜，离市中心近</t>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5607,62 +5607,62 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield Uni Student Hub</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5677,6 +5677,474 @@
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Off the Shelf Festival of Words 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Sheffield（市内多个场地）</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲座)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>5 Nov 2026（周四）16:00–21:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Club/学生夜)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Study Break Crew</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>UoS 优先；⚠️日期待核实</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield Uni Student Hub</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）17:00 开门</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>成人 £5，很便宜，离市中心近</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Huddersfield Uni Student Hub</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/音乐)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>University of Chester</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/万圣节)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -6181,7 +6649,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
     </row>
@@ -6769,7 +7237,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第7轮 已搜/无结果</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -6777,7 +7245,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>计划：第7轮 西北（曼城/兰卡/切斯特）</t>
+          <t>Preston 窗口期内没找到确认过的活动：圣诞亮灯的"Sat 22 Nov"是 2025 年的日期，而且不在窗口内；Guild Hall 还在关闭中；53 Degrees 只找到 10/10 的演出，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -6794,13 +7262,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>顺带匹配（没专门搜）</t>
+          <t>第7轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>未达 3–5 条：搜到的 Lancaster 酒吧巡游和 Woman in Black 都是美国宾州 Lancaster 的，没收录</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6815,15 +7287,15 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第7轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>计划：第7轮 西北（曼城/兰卡/切斯特）</t>
+          <t>未达 3–5 条：圣诞市集 11/18 才开，不在窗口内</t>
         </is>
       </c>
     </row>
@@ -6865,15 +7337,15 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>顺带匹配（没专门搜）</t>
+          <t>第7轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>都是女性向活动，Manchester 还没专门搜</t>
+          <t>包含第1轮的 3 条女性向活动；Project Halloween（Fatsoma）用了模板宣传语，没收录</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7608,10 +8080,34 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>没收录（模板宣传语）</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Project Halloween（Fatsoma，Manchester / Newcastle 两地）："Biggest Halloween Event / 10,000 People"这类宣传语在多个城市的页面上一字不差，按 skill 规则不当作热度依据；也没有其他独立来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>社群空缺</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>University of Lancashire（Preston）：窗口期内没找到确认过的活动，下轮可以试试兰开夏郡范围或 Blackpool</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Cardiff（多个场地）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1425,27 +1425,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>同步发卡迪夫2校</t>
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
@@ -1473,67 +1473,67 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校（RCA 优先）</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London); St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1669,27 +1669,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>同步发伦敦6校</t>
+          <t>同步发伦敦6校（RCA 优先）</t>
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>同步发纽卡斯尔3群</t>
+          <t>同步发伦敦6校</t>
         </is>
       </c>
       <c r="N17" s="2" t="n"/>
@@ -1790,62 +1790,62 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>同步发格拉斯哥3校</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1903,22 +1903,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1946,32 +1946,32 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1981,27 +1981,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>同步发伯明翰3校</t>
+          <t>同步发格拉斯哥3校</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2059,27 +2059,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>第8名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>同步发纽卡斯尔3群</t>
+          <t>同步发伯明翰3校</t>
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13 Nov 2026（周五）19:00</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2137,27 +2137,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>第9名</t>
+          <t>第8名</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>同步发利兹2群</t>
+          <t>同步发纽卡斯尔3群</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
@@ -2175,67 +2175,67 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第9名</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
+          <t>同步发利兹2群</t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Manchester Christmas Markets 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>Snack Finds &amp; Picks; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>免费入场，市中心多个点位，逛吃一条龙</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>同步发 The University of Manchester</t>
+          <t>同步发 Snack Finds &amp; Picks、伯明翰3校</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -2331,17 +2331,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2371,27 +2371,27 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>同步发 UK Food Lovers</t>
+          <t>同步发 The University of Manchester</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -2409,17 +2409,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies</t>
+          <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2429,37 +2429,37 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
+          <t>UK Food Lovers; 伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>同步发 Harper Adams、Wolverhampton</t>
+          <t>同步发 UK Food Lovers</t>
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
@@ -2487,57 +2487,57 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>Harper Adams Campus Life; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Harper Adams、Wolverhampton</t>
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>The Gaming Corner</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2605,22 +2605,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2648,62 +2648,62 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
@@ -2726,32 +2726,32 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2761,27 +2761,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
@@ -2882,32 +2882,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2917,27 +2917,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -2960,32 +2960,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2995,27 +2995,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N33" s="2" t="n"/>
@@ -3033,17 +3033,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3073,22 +3073,22 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3229,22 +3229,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3287,47 +3287,47 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>第4名</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N37" s="2" t="n"/>
@@ -3345,67 +3345,67 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Richmond Family Fireworks</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N38" s="2" t="n"/>
@@ -3428,12 +3428,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3443,42 +3443,42 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3579,37 +3579,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3619,22 +3619,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3735,37 +3735,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Lancaster city centre（历史建筑和街区）</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(灯光艺术节)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3818,57 +3818,57 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Lancaster city centre（历史建筑和街区）</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3891,67 +3891,67 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>运动户外(游泳)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>Swim Wave Tribe</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>第1名</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Platt Fields 就在 Fallowfield</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
+          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
+          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3989,17 +3989,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）20:00–04:00</t>
+          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/House)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4009,27 +4009,27 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
+          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
+          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
+          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Platt Fields 就在 Fallowfield</t>
         </is>
       </c>
       <c r="N46" s="2" t="n"/>
@@ -4052,32 +4052,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Manchester Christmas Markets 2026</t>
+          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
+          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
+          <t>31 Oct 2026（周六）20:00–04:00</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Club/House)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4087,22 +4087,22 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
+          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
+          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>免费入场，市中心多个点位，逛吃一条龙</t>
+          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4130,57 +4130,57 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4208,57 +4208,57 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Girls' Corner; Reel Talk Club</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Manchester 多个场地</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>社交类(女性) + 兴趣类(手工)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4321,22 +4321,22 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4359,62 +4359,62 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Manchester（场地待公布）</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>27 Oct 2026（周二）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
+          <t>社交类(女性交友)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4442,57 +4442,57 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4593,17 +4593,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh's Christmas 2026（开幕）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4613,42 +4613,42 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/节庆)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4676,57 +4676,57 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4754,57 +4754,57 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4827,67 +4827,67 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="2" t="n"/>
@@ -4910,32 +4910,32 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4945,27 +4945,27 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>同步发谢菲尔德2校</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N58" s="2" t="n"/>
@@ -4983,67 +4983,67 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发谢菲尔德2校</t>
         </is>
       </c>
       <c r="N59" s="2" t="n"/>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5101,27 +5101,27 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>同步发 Durham university</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="2" t="n"/>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5159,47 +5159,47 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛马)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Durham university</t>
         </is>
       </c>
       <c r="N61" s="2" t="n"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5237,17 +5237,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(烟花/赛马)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5257,27 +5257,27 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Northumbria 优先</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="n"/>
@@ -5295,17 +5295,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5315,47 +5315,47 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Northumbria 优先</t>
         </is>
       </c>
       <c r="N63" s="2" t="n"/>
@@ -5378,57 +5378,57 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Durham Jazz Festival 2026</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/爵士)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5451,62 +5451,62 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
+          <t>Durham Jazz Festival 2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
+          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(灯光艺术节)</t>
+          <t>年轻人娱乐(Live Music/爵士)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
+          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
+          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
+          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Leeds International Film Festival（第 40 届）</t>
+          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5569,22 +5569,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5612,57 +5612,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
+          <t>Leeds International Film Festival（第 40 届）</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>13 Nov 2026（周五）19:00</t>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5685,37 +5685,37 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5725,22 +5725,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -5768,32 +5768,32 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026（周四）16:00–21:00</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
+          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
+          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
+          <t>5 Nov 2026（周四）16:00–21:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/学生夜)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Study Break Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5881,27 +5881,27 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
+          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
+          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
+          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>UoS 优先；⚠️日期待核实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="2" t="n"/>
@@ -5919,67 +5919,67 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield Uni Student Hub</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
+          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）17:00 开门</t>
+          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(Club/学生夜)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Study Break Crew</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
+          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>成人 £5，很便宜，离市中心近</t>
+          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UoS 优先；⚠️日期待核实</t>
         </is>
       </c>
       <c r="N71" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
+          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
+          <t>7 Nov 2026（周六）17:00 开门</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
+          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
+          <t>成人 £5，很便宜，离市中心近</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6075,32 +6075,32 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>University of Chester</t>
+          <t>Huddersfield Uni Student Hub</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
+          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
+          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）</t>
+          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/万圣节)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6110,27 +6110,27 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
+          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
+          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6145,6 +6145,786 @@
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>University of Chester</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/万圣节)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>St Fagans Halloween Nights（每晚烧 Wicker Man）</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>St Fagans National Museum of History, Cardiff CF5 6XB</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>29–31 Oct 2026，17:30–21:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节) + 本地文化</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>威尔士国家博物馆主办；官方说"门票预计很快售罄"；年年举办</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>https://museum.wales/stfagans/whatson/12647/Halloween-Nights/ ; https://letsgowiththechildren.co.uk/events/halloween-nights-2026-at-st-fagans-national-museum-of-history-cardiff</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff's Winter Wonderland 2026（冰场 / 摩天轮 / 冰壶）</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff Castle, Castle Street, Cardiff CF10 3RB &amp; City Hall Lawn</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(滑冰/游乐)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Visit Cardiff 官方收录，年年举办；Nation.Cymru、Wales247 报道了 2026 年日期</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.visitcardiff.com/christmas/cardiffs-winter-wonderland/ ; https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>城堡里的露天冰场很出片；今年新增冰壶体验</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>威尔士 vs 日本（Nations Championship 橄榄球）</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）16:40 开球</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>运动户外(观赛)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>WRU 官方公布；球场官网有单场售票页</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wru.wales/2026/03/dates-confirmed-for-wales-home-nations-championship-fixtures ; https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-japan/</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>市中心球场，比赛日全城都是气氛；对日本这场的票通常比对新西兰便宜</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>威尔士 vs 新西兰（Nations Championship 橄榄球）</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>14 Nov 2026（周六）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>运动户外(观赛)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>WRU 官方公布；对全黑队是秋季重头戏</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-new-zealand/</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>⚠️对全黑队的票最贵；买不到票也可以去市中心酒吧看直播</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff Christmas Market 2026（附 Queen Street 维多利亚圣诞市集）</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>St John Street / Working Street / Trinity Street / Hills Street / The Hayes, Cardiff city centre（维多利亚市集在 Queen Street）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>12 Nov – 23 Dec 2026（维多利亚市集只在 12–15 Nov）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/美食)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>UK Food Lovers</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>年年举办的市中心圣诞市集；维多利亚市集是 2026 年新增的</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>免费逛；12–15 Nov 这几天两个市集同时开</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>第5名</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff（多个场地）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>第6名</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>斯托克2校 (Staffs Student Life | Stoke / Keele Campus Life)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Trentham Halloween Festival</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Trentham Estate, Stone Road, Trentham, Stoke-on-Trent ST4 8JG</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct – 1 Nov 2026</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(万圣节/户外)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Trentham Estate 官方主办，Visit Staffordshire 收录；有火舞表演、南瓜灯小路、静音 disco</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>https://trentham.co.uk/events/trentham-halloween-festival/ ; https://www.visitstaffordshire.com/event/trentham-halloween-festival/234108101/</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>离 Keele、Staffs 都近；静音 disco 和火舞适合年轻人</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>斯托克2校 (Staffs Student Life | Stoke / Keele Campus Life)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Stoke-on-Trent Comedy Festival（含 Adam Kay、Hannah Byczkowski）</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>King's Hall, Glebe Street, Stoke-on-Trent ST4 1HH</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>13–15 Nov 2026（Adam Kay：14 Nov 20:00）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Study Break Crew</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>市政场馆 King's Hall 主办的喜剧节；Adam Kay（This Is Going to Hurt）是知名巡演喜剧人</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stoke.gov.uk/kingshallevents ; https://www.songkick.com/metro-areas/24537-uk-stoke-on-trent/november-2026</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>周末喜剧节，有好几场可以选；Byczkowski 是《The Traitors》第一季冠军，话题度高</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>斯托克2校 (Staffs Student Life | Stoke / Keele Campus Life)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Big Halloween Street Party（免费）</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Stoke-on-Trent City Centre（Hanley）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）10:00 起</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(万圣节街头活动)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Visit Stoke 官方收录，年年举办的免费街头活动；偏家庭向</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.visitstoke.co.uk/whats-on/the-big-halloween-street-party-p2022331</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>免费，Staffs 在 Hanley 附近；有街头表演和手工市集</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Staffs 优先</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -6532,7 +7312,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
     </row>
@@ -7612,15 +8392,15 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第8轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>计划：第8轮 卡迪夫+斯托克</t>
+          <t>斯托克同城共用；Keele 在 Newcastle-under-Lyme，Trentham 离得最近</t>
         </is>
       </c>
     </row>
@@ -7637,15 +8417,15 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第8轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>计划：第8轮 卡迪夫+斯托克</t>
+          <t>斯托克同城共用；Keele 在 Newcastle-under-Lyme，Trentham 离得最近</t>
         </is>
       </c>
     </row>
@@ -7708,15 +8488,15 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第8轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>计划：第8轮 卡迪夫+斯托克</t>
+          <t>卡迪夫同城共用；两场橄榄球票价偏高，已标注</t>
         </is>
       </c>
     </row>
@@ -7733,15 +8513,15 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第8轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>计划：第8轮 卡迪夫+斯托克</t>
+          <t>卡迪夫同城共用；两场橄榄球票价偏高，已标注</t>
         </is>
       </c>
     </row>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2565,17 +2565,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>Day Trip Buddies</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2585,47 +2585,47 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>University of Stirling; University of St Andrews</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Stirling、St Andrews</t>
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>The Gaming Corner</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2683,22 +2683,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2726,62 +2726,62 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RCA 优先推</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2917,27 +2917,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -2960,32 +2960,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2995,27 +2995,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>RCA Battersea 校区就在旁边</t>
         </is>
       </c>
       <c r="N33" s="2" t="n"/>
@@ -3038,32 +3038,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3073,27 +3073,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>第7名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免费</t>
         </is>
       </c>
       <c r="N34" s="2" t="n"/>
@@ -3111,17 +3111,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>St Mary's University, Twickenham</t>
+          <t>伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第7名</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3229,22 +3229,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3307,22 +3307,22 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>RFU 官方公布的国家队主场赛</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Richmond Family Fireworks</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3365,47 +3365,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>Live Music Crew; 伦敦6校 (UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>离 St Mary's 很近；确认日期之后再推</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>第4名</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N38" s="2" t="n"/>
@@ -3423,67 +3423,67 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>23 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(喜剧)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://byretheatre.com/upcoming/</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>周五晚上的喜剧场，就在校园边上</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️日期待核实</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Centenary Square, Birmingham</t>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3521,42 +3521,42 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UK Food Lovers; Snack Finds &amp; Picks</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3584,32 +3584,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Centenary Square, Birmingham</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3619,22 +3619,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3657,37 +3657,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Harper Adams Campus Life</t>
+          <t>伯明翰3校 (BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花) + 一日游</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
+          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
+          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Wolverhampton Freshers Hub 2026</t>
+          <t>Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Day Trip Buddies; Harper Adams Campus Life</t>
+          <t>Day Trip Buddies; Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3813,37 +3813,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>University of Lancaster</t>
+          <t>Wolverhampton Freshers Hub 2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
+          <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lancaster city centre（历史建筑和街区）</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
+          <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(灯光艺术节)</t>
+          <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Day Trip Buddies; Harper Adams Campus Life</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
+          <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
+          <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
+          <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3896,57 +3896,57 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
+          <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Lancaster city centre（历史建筑和街区）</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>运动户外(游泳)</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Swim Wave Tribe</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+          <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+          <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+          <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>The University of Manchester</t>
+          <t>University of Lancaster</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
+          <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
+          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>运动户外(游泳)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>Swim Wave Tribe</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>第1名</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Platt Fields 就在 Fallowfield</t>
         </is>
       </c>
       <c r="N46" s="2" t="n"/>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
+          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
+          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）20:00–04:00</t>
+          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/House)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4087,27 +4087,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
+          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
+          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
+          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Platt Fields 就在 Fallowfield</t>
         </is>
       </c>
       <c r="N47" s="2" t="n"/>
@@ -4130,32 +4130,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Manchester Christmas Markets 2026</t>
+          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
+          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
+          <t>31 Oct 2026（周六）20:00–04:00</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>年轻人娱乐(Club/House)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
+          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
+          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>免费入场，市中心多个点位，逛吃一条龙</t>
+          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4208,57 +4208,57 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner; Reel Talk Club</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4286,57 +4286,57 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
+          <t>电影/媒体 + 社交类(女性)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Girls' Corner; Reel Talk Club</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Manchester 多个场地</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>27 Oct 2026（周二）</t>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>社交类(女性交友)</t>
+          <t>社交类(女性) + 兴趣类(手工)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4399,22 +4399,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.llgc.co.uk/collections/manchester</t>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4437,62 +4437,62 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Manchester（场地待公布）</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>27 Oct 2026（周二）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
+          <t>社交类(女性交友)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Girls' Corner</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4520,57 +4520,57 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4633,22 +4633,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4671,17 +4671,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>格拉斯哥3校 (Glasgow City College / Glasgow Caledonian University / University of Strathclyde)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh's Christmas 2026（开幕）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4691,42 +4691,42 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/节庆)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4754,57 +4754,57 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4832,57 +4832,57 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4905,67 +4905,67 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>同步发爱丁堡2校</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="n"/>
@@ -4988,32 +4988,32 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>21–31 Oct 2026</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>兴趣类(文学/讲故事)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>爱丁堡2校 (Heriot-Watt University / University of Edinburgh Freshers 2026)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5023,27 +5023,27 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>同步发谢菲尔德2校</t>
+          <t>同步发爱丁堡2校</t>
         </is>
       </c>
       <c r="N59" s="2" t="n"/>
@@ -5061,67 +5061,67 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发谢菲尔德2校</t>
         </is>
       </c>
       <c r="N60" s="2" t="n"/>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5159,17 +5159,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5179,27 +5179,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>同步发 Durham university</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="2" t="n"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5237,47 +5237,47 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛马)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同步发 Durham university</t>
         </is>
       </c>
       <c r="N62" s="2" t="n"/>
@@ -5300,12 +5300,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5315,17 +5315,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(烟花/赛马)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5335,27 +5335,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Northumbria 优先</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N63" s="2" t="n"/>
@@ -5373,17 +5373,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Durham university</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5393,47 +5393,47 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Northumbria 优先</t>
         </is>
       </c>
       <c r="N64" s="2" t="n"/>
@@ -5456,57 +5456,57 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Durham Jazz Festival 2026</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/爵士)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>纽卡斯尔3群 (Newcastle university / Newcastle university 2 / Northumbria university)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5529,62 +5529,62 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
+          <t>Durham Jazz Festival 2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
+          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
+          <t>23–25 Oct 2026</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(灯光艺术节)</t>
+          <t>年轻人娱乐(Live Music/爵士)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
+          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
+          <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
+          <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5612,32 +5612,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Leeds International Film Festival（第 40 届）</t>
+          <t>Light Night Leeds 2026（主题：A City Speaks）</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5647,22 +5647,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+          <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+          <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+          <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5690,57 +5690,57 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
+          <t>Leeds International Film Festival（第 40 届）</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>13 Nov 2026（周五）19:00</t>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -5763,37 +5763,37 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
+          <t>利兹2群 (Leeds Uni Student Hub / Leeds University group 2)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Off the Shelf Festival of Words 2026</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲座)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Page Turners Club</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -5846,32 +5846,32 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>5 Nov 2026（周四）16:00–21:00</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5881,22 +5881,22 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
+          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
+          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -5939,17 +5939,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
+          <t>5 Nov 2026（周四）16:00–21:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/学生夜)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Study Break Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5959,27 +5959,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
+          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
+          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
+          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>UoS 优先；⚠️日期待核实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="n"/>
@@ -5997,67 +5997,67 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield Uni Student Hub</t>
+          <t>谢菲尔德2校 (Sheffield Hallam University / University of Sheffield)</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
+          <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+          <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）17:00 开门</t>
+          <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花)</t>
+          <t>年轻人娱乐(Club/学生夜)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Study Break Crew</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>潜在价值</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
+          <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
+          <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>成人 £5，很便宜，离市中心近</t>
+          <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UoS 优先；⚠️日期待核实</t>
         </is>
       </c>
       <c r="N72" s="2" t="n"/>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
+          <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
+          <t>7 Nov 2026（周六）17:00 开门</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
+          <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
+          <t>成人 £5，很便宜，离市中心近</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6153,32 +6153,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>University of Chester</t>
+          <t>Huddersfield Uni Student Hub</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
+          <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
+          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）</t>
+          <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/万圣节)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6188,27 +6188,27 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
+          <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
+          <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
+          <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6231,17 +6231,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
+          <t>University of Chester</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>St Fagans Halloween Nights（每晚烧 Wicker Man）</t>
+          <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>St Fagans National Museum of History, Cardiff CF5 6XB</t>
+          <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>29–31 Oct 2026，17:30–21:00</t>
+          <t>31 Oct 2026（周六）</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 本地文化</t>
+          <t>年轻人娱乐(烟花/万圣节)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6266,22 +6266,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>高热度</t>
+          <t>中热度</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>威尔士国家博物馆主办；官方说"门票预计很快售罄"；年年举办</t>
+          <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://museum.wales/stfagans/whatson/12647/Halloween-Nights/ ; https://letsgowiththechildren.co.uk/events/halloween-nights-2026-at-st-fagans-national-museum-of-history-cardiff</t>
+          <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
+          <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cardiff's Winter Wonderland 2026（冰场 / 摩天轮 / 冰壶）</t>
+          <t>St Fagans Halloween Nights（每晚烧 Wicker Man）</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Cardiff Castle, Castle Street, Cardiff CF10 3RB &amp; City Hall Lawn</t>
+          <t>St Fagans National Museum of History, Cardiff CF5 6XB</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
+          <t>29–31 Oct 2026，17:30–21:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 本地文化</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Visit Cardiff 官方收录，年年举办；Nation.Cymru、Wales247 报道了 2026 年日期</t>
+          <t>威尔士国家博物馆主办；官方说"门票预计很快售罄"；年年举办</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.visitcardiff.com/christmas/cardiffs-winter-wonderland/ ; https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+          <t>https://museum.wales/stfagans/whatson/12647/Halloween-Nights/ ; https://letsgowiththechildren.co.uk/events/halloween-nights-2026-at-st-fagans-national-museum-of-history-cardiff</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>城堡里的露天冰场很出片；今年新增冰壶体验</t>
+          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>威尔士 vs 日本（Nations Championship 橄榄球）</t>
+          <t>Cardiff's Winter Wonderland 2026（冰场 / 摩天轮 / 冰壶）</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
+          <t>Cardiff Castle, Castle Street, Cardiff CF10 3RB &amp; City Hall Lawn</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）16:40 开球</t>
+          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>WRU 官方公布；球场官网有单场售票页</t>
+          <t>Visit Cardiff 官方收录，年年举办；Nation.Cymru、Wales247 报道了 2026 年日期</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.wru.wales/2026/03/dates-confirmed-for-wales-home-nations-championship-fixtures ; https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-japan/</t>
+          <t>https://www.visitcardiff.com/christmas/cardiffs-winter-wonderland/ ; https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>市中心球场，比赛日全城都是气氛；对日本这场的票通常比对新西兰便宜</t>
+          <t>城堡里的露天冰场很出片；今年新增冰壶体验</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>第3名</t>
+          <t>第2名</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>威尔士 vs 新西兰（Nations Championship 橄榄球）</t>
+          <t>威尔士 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>7 Nov 2026（周六）16:40 开球</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -6505,22 +6505,22 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>WRU 官方公布；对全黑队是秋季重头戏</t>
+          <t>WRU 官方公布；球场官网有单场售票页</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-new-zealand/</t>
+          <t>https://www.wru.wales/2026/03/dates-confirmed-for-wales-home-nations-championship-fixtures ; https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-japan/</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>⚠️对全黑队的票最贵；买不到票也可以去市中心酒吧看直播</t>
+          <t>市中心球场，比赛日全城都是气氛；对日本这场的票通常比对新西兰便宜</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>第4名</t>
+          <t>第3名</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6548,57 +6548,57 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Cardiff Christmas Market 2026（附 Queen Street 维多利亚圣诞市集）</t>
+          <t>威尔士 vs 新西兰（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>St John Street / Working Street / Trinity Street / Hills Street / The Hayes, Cardiff city centre（维多利亚市集在 Queen Street）</t>
+          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>12 Nov – 23 Dec 2026（维多利亚市集只在 12–15 Nov）</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
+          <t>运动户外(观赛)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>UK Food Lovers</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>中热度</t>
+          <t>高热度</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>年年举办的市中心圣诞市集；维多利亚市集是 2026 年新增的</t>
+          <t>WRU 官方公布；对全黑队是秋季重头戏</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+          <t>https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-new-zealand/</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>免费逛；12–15 Nov 这几天两个市集同时开</t>
+          <t>⚠️对全黑队的票最贵；买不到票也可以去市中心酒吧看直播</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>第5名</t>
+          <t>第4名</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6626,32 +6626,32 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
+          <t>Cardiff Christmas Market 2026（附 Queen Street 维多利亚圣诞市集）</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cardiff（多个场地）</t>
+          <t>St John Street / Working Street / Trinity Street / Hills Street / The Hayes, Cardiff city centre（维多利亚市集在 Queen Street）</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
+          <t>12 Nov – 23 Dec 2026（维多利亚市集只在 12–15 Nov）</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>本地生活类(集市/美食)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>UK Food Lovers</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6661,22 +6661,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
+          <t>年年举办的市中心圣诞市集；维多利亚市集是 2026 年新增的</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
+          <t>https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
+          <t>免费逛；12–15 Nov 这几天两个市集同时开</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>第6名</t>
+          <t>第5名</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6699,37 +6699,37 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>斯托克2校 (Staffs Student Life | Stoke / Keele Campus Life)</t>
+          <t>卡迪夫2校 (University of Cardiff / Cardiff Metropolitan University)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Trentham Halloween Festival</t>
+          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Trentham Estate, Stone Road, Trentham, Stoke-on-Trent ST4 8JG</t>
+          <t>Cardiff（多个场地）</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>31 Oct – 1 Nov 2026</t>
+          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(万圣节/户外)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6739,22 +6739,22 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Trentham Estate 官方主办，Visit Staffordshire 收录；有火舞表演、南瓜灯小路、静音 disco</t>
+          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://trentham.co.uk/events/trentham-halloween-festival/ ; https://www.visitstaffordshire.com/event/trentham-halloween-festival/234108101/</t>
+          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>离 Keele、Staffs 都近；静音 disco 和火舞适合年轻人</t>
+          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>第1名</t>
+          <t>第6名</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent Comedy Festival（含 Adam Kay、Hannah Byczkowski）</t>
+          <t>Trentham Halloween Festival</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>King's Hall, Glebe Street, Stoke-on-Trent ST4 1HH</t>
+          <t>Trentham Estate, Stone Road, Trentham, Stoke-on-Trent ST4 8JG</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Adam Kay：14 Nov 20:00）</t>
+          <t>31 Oct – 1 Nov 2026</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>年轻人娱乐(喜剧)</t>
+          <t>年轻人娱乐(万圣节/户外)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Study Break Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6817,22 +6817,22 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>市政场馆 King's Hall 主办的喜剧节；Adam Kay（This Is Going to Hurt）是知名巡演喜剧人</t>
+          <t>Trentham Estate 官方主办，Visit Staffordshire 收录；有火舞表演、南瓜灯小路、静音 disco</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://www.stoke.gov.uk/kingshallevents ; https://www.songkick.com/metro-areas/24537-uk-stoke-on-trent/november-2026</t>
+          <t>https://trentham.co.uk/events/trentham-halloween-festival/ ; https://www.visitstaffordshire.com/event/trentham-halloween-festival/234108101/</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>周末喜剧节，有好几场可以选；Byczkowski 是《The Traitors》第一季冠军，话题度高</t>
+          <t>离 Keele、Staffs 都近；静音 disco 和火舞适合年轻人</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>第2名</t>
+          <t>第1名</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -6860,62 +6860,62 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Big Halloween Street Party（免费）</t>
+          <t>Stoke-on-Trent Comedy Festival（含 Adam Kay、Hannah Byczkowski）</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent City Centre（Hanley）</t>
+          <t>King's Hall, Glebe Street, Stoke-on-Trent ST4 1HH</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）10:00 起</t>
+          <t>13–15 Nov 2026（Adam Kay：14 Nov 20:00）</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>本地生活类(万圣节街头活动)</t>
+          <t>年轻人娱乐(喜剧)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>Study Break Crew</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>市政场馆 King's Hall 主办的喜剧节；Adam Kay（This Is Going to Hurt）是知名巡演喜剧人</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stoke.gov.uk/kingshallevents ; https://www.songkick.com/metro-areas/24537-uk-stoke-on-trent/november-2026</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>周末喜剧节，有好几场可以选；Byczkowski 是《The Traitors》第一季冠军，话题度高</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Visit Stoke 官方收录，年年举办的免费街头活动；偏家庭向</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.visitstoke.co.uk/whats-on/the-big-halloween-street-party-p2022331</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>免费，Staffs 在 Hanley 附近；有街头表演和手工市集</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>第3名</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>Staffs 优先</t>
         </is>
       </c>
       <c r="N83" s="2" t="n"/>
@@ -6925,6 +6925,1020 @@
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>斯托克2校 (Staffs Student Life | Stoke / Keele Campus Life)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Big Halloween Street Party（免费）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Stoke-on-Trent City Centre（Hanley）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026（周六）10:00 起</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(万圣节街头活动)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Visit Stoke 官方收录，年年举办的免费街头活动；偏家庭向</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.visitstoke.co.uk/whats-on/the-big-halloween-street-party-p2022331</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>免费，Staffs 在 Hanley 附近；有街头表演和手工市集</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Staffs 优先</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>University of St Andrews</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Alan Carr 单口喜剧巡演 @ Byre Theatre</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>20 Oct 2026（周二）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>知名喜剧人巡演场；Byre 是 St Andrews 大学主办的剧院，官方活动日历有列出；小剧场，座位少</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>https://byretheatre.com/upcoming/ ; https://events.st-andrews.ac.uk/event-location/byre/</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>在小镇能看到一线喜剧人很难得，就在校园边上；座位有限，要早买</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>University of St Andrews</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>University of Stirling; Day Trip Buddies</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>University of St Andrews</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>23 Oct 2026（周五）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>https://byretheatre.com/upcoming/</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>周五晚上的喜剧场，就在校园边上</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>University of St Andrews</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Byre Theatre 周四电影放映</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>29 Oct / 5 Nov / 12 Nov 2026（都是周四）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>大学剧院固定的放映场，官方节目单有列出</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>https://byretheatre.com/upcoming/film/</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>便宜又方便的学习间隙放松，片单看官网</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>University of Stirling</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>University of St Andrews; Day Trip Buddies</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>University of Stirling</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Witch Hunt（以苏格兰女巫审判为题材的新音乐剧）</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Macrobert Arts Centre, University of Stirling, Stirling FK9 4LA</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>17 Oct 2026（周六）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>兴趣类(剧场/音乐剧)</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Macrobert Arts Centre 秋季节目单有列出（在 Stirling 大学校园里）</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.whatsonstirling.co.uk/listings/macrobert-arts-centre/ ; https://www.macrobertartscentre.org/</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>就在 Stirling 校园里；万圣节季看苏格兰女巫题材正应景</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>就在校园里</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>University of Stirling</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Briarlands Farm Bonfire Night</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Briarlands Farm, Stirling（Cambusbarron / Craigforth 一带，具体地址见官网）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>What's On Stirling 收录，农场年年办的篝火夜；没有售票数据（Facebook 上搜到的"Sat 1 Nov"帖子是 2025 年的）</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.whatsonstirling.co.uk/event/109377-briarlands-farm-bonfire-night/ ; https://briarlandsfarm.co.uk/events/</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Stirling 本地的篝火夜，离校园近</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="n"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>University of Aberdeen Freshers 2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>soundfestival 2026（新音乐节）</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>The Lemon Tree / Cowdray Hall / King's Pavilion 等，Aberdeen &amp; Aberdeenshire</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>22–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/实验音乐)</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Creative Scotland 官方报道 2026 年节目；欧洲知名的新音乐节，年年举办；有一场在前核掩体里</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.creativescotland.com/news-stories/latest-news/archive/2026/08/acclaimed-new-music-festival-reveals-details-of-2026-edition ; https://sound-scotland.co.uk/</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>街头表演、声音漫步、装置艺术，形式新鲜，很多场免费或便宜</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>University of Aberdeen Freshers 2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen Fireworks Night（市议会主办）</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen Beach / Beach Boulevard 一带（往年因海滩施工改在 North Pier 燃放）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>⚠️每年固定 5 Nov（2026 年是周四）19:30；2026 年的官方公告还没看到</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen 市议会年年主办的免费烟花；Press and Journal 每年都有报道</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aberdeencity.gov.uk/node/8869 ; https://www.pressandjournal.co.uk/fp/news/6869573/all-you-need-to-know-aberdeen-fireworks-2025/</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>免费；推之前确认一下 2026 年的官方公告和燃放地点</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>⚠️2026 年公告待确认</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>University of Aberdeen Freshers 2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen Christmas Village 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Broad Street, Aberdeen city centre</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/节庆)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen 市议会、Aberdeen Inspired 主办，年年举办</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aberdeeninspired.com/festival/aberdeen-christmas-market/christmas-village ; https://www.aberdeencity.gov.uk/news/christmas-village-launches-citys-festive-celebrations</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>市中心免费逛，开幕那周就能去</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>University of West of Scotland</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Paisley Halloween Festival 2026（主题：Haunted House）</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Paisley town centre（游行路线经过 Mill Street）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>23 Oct（周五 16:00 起）– 24 Oct 2026（周六 14:00 起），每晚 19:00 游行</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>本地生活类(万圣节节庆)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Renfrewshire 市议会 2026 年官方新闻确认；苏格兰最大的万圣节节庆之一，年年举办；免费</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.renfrewshire.gov.uk/news/2026/paisley-halloween-festival-return-next-month ; https://paisley.is/featured_event/halloween/</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>免费，UWS Paisley 校区就在镇中心；有灯光游行和夜市</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="n"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>University of West of Scotland</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥3校</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Paisley 到格拉斯哥约 15 分钟火车</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -7095,7 +8109,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
     </row>
@@ -7216,7 +8230,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7571,15 +8585,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第9轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>计划：第9轮 苏格兰其余学校</t>
+          <t>Big Hoolie（圣安德鲁日）在 11/28，不在窗口内；St Andrews Voices 节 2024 年后没看到还在办</t>
         </is>
       </c>
     </row>
@@ -7621,15 +8635,15 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第9轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>计划：第9轮 苏格兰其余学校</t>
+          <t>未达 3–5 条：只搜了 Paisley 校区；Ayr、Lanarkshire、Dumfries 校区没单独搜</t>
         </is>
       </c>
     </row>
@@ -7746,17 +8760,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第9轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>计划：第9轮 苏格兰其余学校</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8563,15 +9573,15 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>第9轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>计划：第9轮 苏格兰其余学校</t>
+          <t>海滩烟花 2026 年的官方公告还没看到</t>
         </is>
       </c>
     </row>
@@ -8586,7 +9596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8884,10 +9894,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>日期待核实</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen Fireworks Night：每年固定 5 Nov，但 2026 年的官方公告还没看到</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批；另外该社群本来就缺可靠的带日期信源</t>
+          <t>本期到第 9 轮结束；该社群本来就缺可靠的带日期信源</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>计划：第12轮起按兴趣分批</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>计划：第10轮 中部其余学校</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>计划：第10轮 中部其余学校</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>计划：第11轮 约克+赫尔</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>计划：第11轮 约克+赫尔</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>未搜（留给后续轮次）</t>
+          <t>未搜（用户决定本期不搜）</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>计划：第10轮 中部其余学校</t>
+          <t>本期到第 9 轮结束</t>
         </is>
       </c>
     </row>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -13,7 +13,7 @@
     <sheet name="待核实与缺口" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Track B 30天活动'!$A$1:$O$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Track B 30天活动'!$A$1:$O$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'社群覆盖清单'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核实与缺口'!$A$1:$B$26</definedName>
   </definedNames>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -621,13 +621,13 @@
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: GAMING 👇
-🎮 EPIC.LAN, Kettering — the UK's biggest LAN party with a CS2 tournament, 29 Oct–1 Nov.
+🎮 EPIC49 LAN, Kettering — a 700-seat LAN party with CS2, VALORANT, StarCraft II &amp; osu! tournaments, 29 Oct–1 Nov.
 🦸 MCM Comic Con, London ExCeL — gaming, anime &amp; cosplay all weekend, 23–25 Oct.</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>EPIC.LAN 秋季 LAN Party（EPIC48）+ CS2 锦标赛</t>
+          <t>EPIC49 LAN Party（含 CS2 / VALORANT / StarCraft II / osu! 锦标赛）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>29 Oct 16:00 – 1 Nov 16:00 2026（CS2 赛程 30 Oct–1 Nov）</t>
+          <t>29 Oct 16:00 – 1 Nov 16:00 2026（锦标赛在 30 Oct – 1 Nov）</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
@@ -657,22 +657,22 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>英国最大 LAN 系列，已办到第 48 届，多年连续举办；CS2 赛上限 48 队、奖池最高 £6,500、ASUS ROG 冠名（均来自官方赛事页）</t>
+          <t>英国老牌 LAN 系列，已办到第 49 届，每年两届；这届 700 个电脑位；官网有 EPIC49 专页，赛事项目包括 CS2 和 VALORANT</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>https://tournaments.epiclan.co.uk/tournaments/epic48-cs2 ; https://www.epiclan.co.uk/events ; https://liquipedia.net/counterstrike/EPIC.LAN/48</t>
+          <t>https://www.epiclan.co.uk/epic49 ; https://www.yorkshirepudd.co.uk/epic49-kettering-lan/ ; https://esportsinsider.com/2025/07/epic-lan-unveils-dates-for-2026-events</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>英国线下 CS2 最正规的草根赛事，可组队参赛或自带电脑去玩；注意：CS2 报名已于 7/16 截止，现在只能买 LAN 入场票；票价未核实，可能偏高；个别页面写作"EPIC49"，届数需再确认</t>
+          <t>自带电脑参加 4 天 LAN；报比赛必须买 BYOC 票，而且一张票只能报一个项目；万圣节夜有社区派对；票价没核实</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>CS2 Frag Hub / Valorant Riot Crew</t>
+          <t>CS2 Frag Hub；Valorant Riot Crew</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>CS2 Frag Hub / Valorant Riot Crew</t>
+          <t>CS2 Frag Hub</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -765,13 +765,13 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
-This month: ESPORTS &amp; LAN 👇
-🎮 EPIC.LAN, Kettering — the UK's biggest LAN party with a CS2 tournament, 29 Oct–1 Nov.</t>
+This month: CS2 &amp; LAN 👇
+🔫 EPIC49 LAN, Kettering — 4 days of LAN with a CS2 tournament (BYOC ticket needed), 29 Oct–1 Nov.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>EPIC.LAN 秋季 LAN Party（EPIC48）+ CS2 锦标赛</t>
+          <t>EPIC49 LAN Party（含 CS2 / VALORANT / StarCraft II / osu! 锦标赛）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>29 Oct 16:00 – 1 Nov 16:00 2026（CS2 赛程 30 Oct–1 Nov）</t>
+          <t>29 Oct 16:00 – 1 Nov 16:00 2026（锦标赛在 30 Oct – 1 Nov）</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -801,22 +801,22 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>英国最大 LAN 系列，已办到第 48 届，多年连续举办；CS2 赛上限 48 队、奖池最高 £6,500、ASUS ROG 冠名（均来自官方赛事页）</t>
+          <t>英国老牌 LAN 系列，已办到第 49 届，每年两届；这届 700 个电脑位；官网有 EPIC49 专页，赛事项目包括 CS2 和 VALORANT</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>https://tournaments.epiclan.co.uk/tournaments/epic48-cs2 ; https://www.epiclan.co.uk/events ; https://liquipedia.net/counterstrike/EPIC.LAN/48</t>
+          <t>https://www.epiclan.co.uk/epic49 ; https://www.yorkshirepudd.co.uk/epic49-kettering-lan/ ; https://esportsinsider.com/2025/07/epic-lan-unveils-dates-for-2026-events</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>英国线下 CS2 最正规的草根赛事，可组队参赛或自带电脑去玩；注意：CS2 报名已于 7/16 截止，现在只能买 LAN 入场票；票价未核实，可能偏高；个别页面写作"EPIC49"，届数需再确认</t>
+          <t>自带电脑参加 4 天 LAN；报比赛必须买 BYOC 票，而且一张票只能报一个项目；万圣节夜有社区派对；票价没核实</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>The Gaming Corner；Valorant Riot Crew</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
@@ -2587,15 +2587,94 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Valorant Riot Crew</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>待制作：Valorant Riot Crew.png</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>🔍 Event Radar (UK) — what's worth doing this month.
+This month: VALORANT &amp; LAN 👇
+🎯 EPIC49 LAN, Kettering — 4 days of LAN with a VALORANT tournament (BYOC ticket needed), 29 Oct–1 Nov.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>EPIC49 LAN Party（含 CS2 / VALORANT / StarCraft II / osu! 锦标赛）</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Kettering Leisure Village, Kettering, Northamptonshire</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>29 Oct 16:00 – 1 Nov 16:00 2026（锦标赛在 30 Oct – 1 Nov）</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(电竞/LAN)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>英国老牌 LAN 系列，已办到第 49 届，每年两届；这届 700 个电脑位；官网有 EPIC49 专页，赛事项目包括 CS2 和 VALORANT</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.epiclan.co.uk/epic49 ; https://www.yorkshirepudd.co.uk/epic49-kettering-lan/ ; https://esportsinsider.com/2025/07/epic-lan-unveils-dates-for-2026-events</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>自带电脑参加 4 天 LAN；报比赛必须买 BYOC 票，而且一张票只能报一个项目；万圣节夜有社区派对；票价没核实</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>The Gaming Corner；CS2 Frag Hub</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>待制作：UCL Hub.png</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: LONDON &amp; CAMPUS 👇
@@ -2608,119 +2687,54 @@
 🎃 Skindred Halloween Special, Alexandra Palace — with Alien Ant Farm, Spineshank &amp; Orgy, 31 Oct.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>MCM Comic Con London（October 2026）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>23–25 Oct 2026</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>兴趣类(游戏/动漫/流行文化)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>The Gaming Corner</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>电影/媒体</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
@@ -2740,27 +2754,27 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -2770,22 +2784,22 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
@@ -2805,27 +2819,27 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -2835,22 +2849,22 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
@@ -2870,12 +2884,12 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2885,12 +2899,12 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -2900,22 +2914,22 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Live Music Crew；St Mary's University, Twickenham</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
@@ -2935,27 +2949,27 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -2965,22 +2979,22 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew；St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
@@ -3000,77 +3014,142 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>本地生活类(城市传统活动)</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
           <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr">
         <is>
           <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr">
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N37" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O37" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>University of St Andrews</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>待制作：University of St Andrews.png</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: ST ANDREWS 👇
@@ -3080,119 +3159,54 @@
 🎞️ Byre Thursday Films, St Andrews — easy study-break screenings, 29 Oct / 5 &amp; 12 Nov.</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Alan Carr 单口喜剧巡演 @ Byre Theatre</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>20 Oct 2026（周二）</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(喜剧)</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>知名喜剧人巡演场；Byre 是 St Andrews 大学主办的剧院，官方活动日历有列出；小剧场，座位少</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>https://byretheatre.com/upcoming/ ; https://events.st-andrews.ac.uk/event-location/byre/</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>在小镇能看到一线喜剧人很难得，就在校园边上；座位有限，要早买</t>
         </is>
       </c>
-      <c r="M37" s="8" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>Day Trip Buddies；University of Stirling</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
@@ -3212,12 +3226,12 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
+          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3227,37 +3241,37 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>23 Oct 2026（周五）</t>
+          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(喜剧)</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
+          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
+          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>https://byretheatre.com/upcoming/</t>
+          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>周五晚上的喜剧场，就在校园边上</t>
+          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Day Trip Buddies；University of Stirling</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
@@ -3277,77 +3291,142 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>23 Oct 2026（周五）</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>https://byretheatre.com/upcoming/</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>周五晚上的喜剧场，就在校园边上</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
           <t>Byre Theatre 周四电影放映</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>29 Oct / 5 Nov / 12 Nov 2026（都是周四）</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>电影/媒体</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>大学剧院固定的放映场，官方节目单有列出</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>https://byretheatre.com/upcoming/film/</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t>便宜又方便的学习间隙放松，片单看官网</t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr">
+      <c r="M41" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr">
+      <c r="N41" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O41" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>待制作：Glasgow City College.png</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: GLASGOW NIGHTS 👇
@@ -3356,119 +3435,54 @@
 🎸 Pop Mutations x Tiny Changes, Glasgow — an indie weekender across four grassroots venues, 13–14 Nov.</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
-      <c r="M41" s="8" t="inlineStr">
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t>University of West of Scotland</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
@@ -3488,77 +3502,142 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(Live Music/金属)</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>Live Music Crew</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>13–14 Nov 2026</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="M44" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="N44" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O44" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>University of West of Scotland</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>待制作：University of West of Scotland.png</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: PAISLEY &amp; GLASGOW 👇
@@ -3566,144 +3645,144 @@
 🎃 Paisley Halloween Festival, Paisley — a free Haunted House parade &amp; night market, 23–24 Oct.</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(沉浸式/万圣节)</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr">
+      <c r="M45" s="8" t="inlineStr">
         <is>
           <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="N45" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O45" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Paisley Halloween Festival 2026（主题：Haunted House）</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Paisley town centre（游行路线经过 Mill Street）</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>23 Oct（周五 16:00 起）– 24 Oct 2026（周六 14:00 起），每晚 19:00 游行</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>本地生活类(万圣节节庆)</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Renfrewshire 市议会 2026 年官方新闻确认；苏格兰最大的万圣节节庆之一，年年举办；免费</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>https://www.renfrewshire.gov.uk/news/2026/paisley-halloween-festival-return-next-month ; https://paisley.is/featured_event/halloween/</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>免费，UWS Paisley 校区就在镇中心；有灯光游行和夜市</t>
         </is>
       </c>
-      <c r="M45" s="8" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr">
+      <c r="N46" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O46" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>待制作：Heriot-Watt University.png</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: EDINBURGH 👇
@@ -3712,119 +3791,54 @@
 🎞️ Edinburgh Short Film Festival, Edinburgh — bite-size screenings for film lovers, 6–22 Nov.</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Edinburgh's Christmas 2026（开幕）</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>East &amp; West Princes Street Gardens / George Street, Edinburgh</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>14 Nov 2026 – 3 Jan 2027（窗口内只有 14–15 Nov 开幕周末）</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>本地生活类(集市/节庆)</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>爱丁堡官方冬季节庆，每年举办；免费入场、不用买票</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>https://edinburgh.org/festivals/edinburghs-christmas/ ; https://edwinterfest.com/edinburgh-christmas/whats-on/traditional-christmas-markets</t>
         </is>
       </c>
-      <c r="L46" s="8" t="inlineStr">
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>开幕周末可以去；市集免费逛，每天 10:00–22:00</t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
+      <c r="M47" s="8" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>21–31 Oct 2026</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>兴趣类(文学/讲故事)</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
-        </is>
-      </c>
-      <c r="M47" s="8" t="inlineStr">
-        <is>
-          <t>Page Turners Club</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
@@ -3844,77 +3858,142 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Page Turners Club</t>
+        </is>
+      </c>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
           <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Edinburgh（多个场地）</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>电影/媒体</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
-      <c r="K48" s="8" t="inlineStr">
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L49" s="8" t="inlineStr">
         <is>
           <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
+      <c r="M49" s="8" t="inlineStr">
         <is>
           <t>Reel Talk Club</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr">
+      <c r="N49" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O49" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>University of Stirling</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>待制作：University of Stirling.png</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: STIRLING 👇
@@ -3923,119 +4002,54 @@
 🎭 Witch Hunt (new musical), Macrobert Arts Centre, Stirling — Scottish witch trials on stage, on campus, 17 Oct.</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花/赛车) + 一日游</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
         </is>
       </c>
-      <c r="L49" s="8" t="inlineStr">
+      <c r="L50" s="8" t="inlineStr">
         <is>
           <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
         </is>
       </c>
-      <c r="M49" s="8" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>Day Trip Buddies；University of St Andrews</t>
-        </is>
-      </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O49" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Briarlands Farm Bonfire Night</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Briarlands Farm, Stirling（Cambusbarron / Craigforth 一带，具体地址见官网）</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>7 Nov 2026（周六）</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(烟花)</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="inlineStr">
-        <is>
-          <t>What's On Stirling 收录，农场年年办的篝火夜；没有售票数据（Facebook 上搜到的"Sat 1 Nov"帖子是 2025 年的）</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>https://www.whatsonstirling.co.uk/event/109377-briarlands-farm-bonfire-night/ ; https://briarlandsfarm.co.uk/events/</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>Stirling 本地的篝火夜，离校园近</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
@@ -4055,77 +4069,142 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>Briarlands Farm Bonfire Night</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Briarlands Farm, Stirling（Cambusbarron / Craigforth 一带，具体地址见官网）</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>7 Nov 2026（周六）</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>What's On Stirling 收录，农场年年办的篝火夜；没有售票数据（Facebook 上搜到的"Sat 1 Nov"帖子是 2025 年的）</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>https://www.whatsonstirling.co.uk/event/109377-briarlands-farm-bonfire-night/ ; https://briarlandsfarm.co.uk/events/</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>Stirling 本地的篝火夜，离校园近</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
           <t>Witch Hunt（以苏格兰女巫审判为题材的新音乐剧）</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Macrobert Arts Centre, University of Stirling, Stirling FK9 4LA</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>17 Oct 2026（周六）</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>兴趣类(剧场/音乐剧)</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Macrobert Arts Centre 秋季节目单有列出（在 Stirling 大学校园里）</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>https://www.whatsonstirling.co.uk/listings/macrobert-arts-centre/ ; https://www.macrobertartscentre.org/</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr">
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>就在 Stirling 校园里；万圣节季看苏格兰女巫题材正应景</t>
         </is>
       </c>
-      <c r="M51" s="8" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr">
+      <c r="N52" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O52" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>待制作：BCU Fresher Hub 2026.png</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: BIRMINGHAM 👇
@@ -4134,119 +4213,54 @@
 🤘 Skindred, O2 Academy Birmingham — a rock night on Halloween eve, 30 Oct.</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>本地生活类(集市/美食)</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
-      <c r="M52" s="8" t="inlineStr">
+      <c r="M53" s="8" t="inlineStr">
         <is>
           <t>Snack Finds &amp; Picks；UK Food Lovers</t>
-        </is>
-      </c>
-      <c r="N52" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O52" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Centenary Square, Birmingham</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(滑冰/游乐)</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
-        </is>
-      </c>
-      <c r="M53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
@@ -4266,156 +4280,221 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>Birmingham Big Wheel &amp; Ice Rink（Centenary Square）</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Centenary Square, Birmingham</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>5 Nov 2026 – 3 Jan 2027，每天 10:00–22:00</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(滑冰/游乐)</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>跟圣诞市集同期，市集官方配套项目，年年举办；没有售票数据</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>https://www.birmingham-now.co.uk/news/26551457.birmingham-frankfurt-christmas-market-2026---need-know/</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>BCU 主校区附近，适合宿舍、群友组团去滑冰</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
           <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>30 Oct 2026（周五）</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
         </is>
       </c>
-      <c r="K54" s="8" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L55" s="8" t="inlineStr">
         <is>
           <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
-      <c r="M54" s="8" t="inlineStr">
+      <c r="M55" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
+      <c r="N55" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O55" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Wolverhampton Freshers Hub 2026 / Harper Adams Campus Life</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>待制作：Wolverhampton Freshers Hub 2026.png</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: BONFIRE NIGHT 👇
 🔥 Weston Park Bonfire Night, Shifnal — a giant bonfire, two fireworks shows and a funfair, 8 Nov.</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Weston Park Bonfire &amp; Fireworks Night 2026</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>8 Nov 2026（周日）15:00 开门，17:00 点篝火，18:00 和 19:30 两场烟花</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花) + 一日游</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>年年举办的庄园篝火夜，在 See Tickets / Ents24 正规售票，Visit Telford 有收录</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>https://weston-park.com/bonfire-fireworks-night/ ; https://www.seetickets.com/event/bonfire-fireworks-night-2026/weston-park/3697208</t>
         </is>
       </c>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="L56" s="8" t="inlineStr">
         <is>
           <t>离 Harper Adams 和 Wolverhampton 都不远；乡村庄园 + 游乐场 + 两场烟花，适合当一日游</t>
         </is>
       </c>
-      <c r="M55" s="8" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>Day Trip Buddies</t>
         </is>
       </c>
-      <c r="N55" s="8" t="inlineStr">
+      <c r="N56" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O56" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Sheffield Hallam University / University of Sheffield</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>待制作：Sheffield Hallam University.png</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: SHEFFIELD 👇
@@ -4424,119 +4503,54 @@
 🎃 Leadmill Fridays Halloween Special, The Foundry, Sheffield — the classic student night goes spooky (date TBC), Halloween Fri.</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
+      <c r="L57" s="8" t="inlineStr">
         <is>
           <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
-      <c r="M56" s="8" t="inlineStr">
+      <c r="M57" s="8" t="inlineStr">
         <is>
           <t>Page Turners Club</t>
-        </is>
-      </c>
-      <c r="N56" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O56" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>5 Nov 2026（周四）16:00–21:00</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(烟花)</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
-        <is>
-          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
-        </is>
-      </c>
-      <c r="M57" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
@@ -4556,77 +4570,142 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
+          <t>ArcNight 2026：谢菲尔德篝火夜烟花</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Don Valley Bowl, Coleridge Road, Sheffield S9 2DF</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>5 Nov 2026（周四）16:00–21:00</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花)</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>新办的活动，由 Illuminate the Gardens 团队主办；Exposed Magazine、Yorkshire Live 报道；票价还没公布</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>https://arcnight.com/ ; https://www.exposedmagazine.co.uk/whats-new/brand-new-bonfire-night-spectacular-to-bring-sheffield-steel-to-the-sky-at-don-valley/</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>谢菲尔德唯一的大型烟花，篝火夜正日子；有电车可以到</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
           <t>Leadmill Fridays 万圣节特别场 @ The Foundry</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>The Foundry, Sheffield Students' Union, Western Bank, Sheffield S10 2TG</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>⚠️万圣节前的周五（推定 30 Oct 2026），活动页没写年份，待核实</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Club/学生夜)</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>Leadmill 是谢菲尔德老牌学生夜品牌，主办方说"经常售罄"；在 Skiddle 售票</t>
         </is>
       </c>
-      <c r="K58" s="8" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>https://leadmill.co.uk/event/leadmill-fridays-halloween-special-at-the-foundry/ ; https://www.skiddle.com/whats-on/Sheffield/halloween-events/</t>
         </is>
       </c>
-      <c r="L58" s="8" t="inlineStr">
+      <c r="L59" s="8" t="inlineStr">
         <is>
           <t>专门办给学生的万圣节夜，就在 UoS 学生会里；日期确认后再推</t>
         </is>
       </c>
-      <c r="M58" s="8" t="inlineStr">
+      <c r="M59" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr">
+      <c r="N59" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O59" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>St Mary's University, Twickenham</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>待制作：St Mary's University, Twickenham.png</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: TWICKENHAM &amp; SW LONDON 👇
@@ -4636,119 +4715,54 @@
 🎆 Richmond Family Fireworks, Richmond — local fireworks &amp; funfair (date TBC), early Nov.</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I60" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J59" s="8" t="inlineStr">
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
-      <c r="K59" s="8" t="inlineStr">
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
-      <c r="L59" s="8" t="inlineStr">
+      <c r="L60" s="8" t="inlineStr">
         <is>
           <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
-      <c r="M59" s="8" t="inlineStr">
+      <c r="M60" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew；UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O59" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>8 Nov 2026（周日）</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>运动户外(观赛)</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="inlineStr">
-        <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
-        </is>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
-        </is>
-      </c>
-      <c r="M60" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
@@ -4768,7 +4782,7 @@
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+          <t>英格兰 vs 澳大利亚（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -4783,7 +4797,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>8 Nov 2026（周日）</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -4798,17 +4812,17 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>RFU 官方公布的国家队主场赛</t>
+          <t>RFU 官方公布的国家队主场赛，是新赛事 Nations Championship 的首届</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship ; https://allianzstadiumtwickenham.com/nations-championship</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+          <t>St Mary's 是体育强校，球场就在家门口；⚠️国家队比赛票价偏高</t>
         </is>
       </c>
       <c r="M61" s="8" t="inlineStr">
@@ -4833,77 +4847,142 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
+          <t>英格兰 vs 日本（Nations Championship 橄榄球）</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Allianz Stadium Twickenham, 200 Whitton Road, Twickenham TW2 7BA</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>14 Nov 2026（周六）</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>运动户外(观赛)</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>RFU 官方公布的国家队主场赛</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.englandrugby.com/follow/news-and-media/england-fixtures-confirmed-inaugural-nations-championship</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>对日本这场的票通常比对新西兰、澳大利亚便宜，更适合学生；⚠️票价还是要看一下</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
           <t>Richmond Family Fireworks</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Richmond Athletic Ground, Twickenham Road, Richmond TW9 2SF</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>⚠️待核实：一个来源写 1 Nov，另一个写 5–7 Nov 2026</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J62" s="8" t="inlineStr">
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>年年举办的本地烟花会（Richmond Athletic Association 主办）；2026 年日期各来源说法不一，所以降级</t>
         </is>
       </c>
-      <c r="K62" s="8" t="inlineStr">
+      <c r="K63" s="8" t="inlineStr">
         <is>
           <t>https://www.rag-events.co.uk/major-public-events-at-the-rag/richmond-family-fireworks/ ; https://chiswicktoday.co.uk/chiswick-fireworks-bonfire-night/</t>
         </is>
       </c>
-      <c r="L62" s="8" t="inlineStr">
+      <c r="L63" s="8" t="inlineStr">
         <is>
           <t>离 St Mary's 很近；确认日期之后再推</t>
         </is>
       </c>
-      <c r="M62" s="8" t="inlineStr">
+      <c r="M63" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr">
+      <c r="N63" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>University of Lancaster</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>待制作：University of Lancaster.png</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: LANCASTER 👇
@@ -4911,223 +4990,223 @@
 🏊 Capernwray Lake Swim, Carnforth — a late-season open-water swim (cold-water experience needed), 31 Oct.</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Light Up Lancaster 2026（主题：No Boundaries）</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Lancaster city centre（历史建筑和街区）</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>5–7 Nov 2026（周四到周六）17:00–22:00</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J63" s="8" t="inlineStr">
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>Light Up the North 联盟成员，年年举办；Lancaster BID、Visit Lancashire、Lancaster Guardian、Beyond Radio 都有报道</t>
         </is>
       </c>
-      <c r="K63" s="8" t="inlineStr">
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>https://www.lightuplancaster.co.uk/ ; https://www.beyond.radio/news/local-news/light-up-lancaster-promises-to-illuminate-city-with-no-boundaries/ ; https://www.facebook.com/lightuplancaster/</t>
         </is>
       </c>
-      <c r="L63" s="8" t="inlineStr">
+      <c r="L64" s="8" t="inlineStr">
         <is>
           <t>免费的灯光艺术路线，连着三晚，下课后去逛正合适</t>
         </is>
       </c>
-      <c r="M63" s="8" t="inlineStr">
+      <c r="M64" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr">
+      <c r="N64" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O64" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>运动户外(游泳)</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr">
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
         </is>
       </c>
-      <c r="K64" s="8" t="inlineStr">
+      <c r="K65" s="8" t="inlineStr">
         <is>
           <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
         </is>
       </c>
-      <c r="L64" s="8" t="inlineStr">
+      <c r="L65" s="8" t="inlineStr">
         <is>
           <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
         </is>
       </c>
-      <c r="M64" s="8" t="inlineStr">
+      <c r="M65" s="8" t="inlineStr">
         <is>
           <t>Swim Wave Tribe</t>
         </is>
       </c>
-      <c r="N64" s="8" t="inlineStr">
+      <c r="N65" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O65" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>University of Chester</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>待制作：University of Chester.png</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: CHESTER 👇
 🎃 Lord Mayor's Spooktacular Fireworks, Chester Racecourse — Halloween fireworks, rides &amp; fire performers, 31 Oct.</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>The Lord Mayor's Spooktacular Fireworks（切斯特赛马场万圣节烟花）</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Chester Racecourse, Watergate Square, Chester CH1 2LY</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026（周六）</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花/万圣节)</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J65" s="8" t="inlineStr">
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>赛马场官方主办，年年举办的市长烟花会，今年提前到万圣节并改成万圣节主题（Chester Standard、Chester Online 报道）</t>
         </is>
       </c>
-      <c r="K65" s="8" t="inlineStr">
+      <c r="K66" s="8" t="inlineStr">
         <is>
           <t>https://www.chester-races.com/whats-on/the-lord-mayors-spooctacular-fireworks/ ; https://chesteronline.co.uk/chester-fireworks-bonfire-night/</t>
         </is>
       </c>
-      <c r="L65" s="8" t="inlineStr">
+      <c r="L66" s="8" t="inlineStr">
         <is>
           <t>市中心赛马场，有游乐设施、踩高跷、火舞表演；是切斯特窗口期内唯一确认的大活动</t>
         </is>
       </c>
-      <c r="M65" s="8" t="inlineStr">
+      <c r="M66" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr">
+      <c r="N66" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O66" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>待制作：The University of Manchester.png</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: MANCHESTER 👇
@@ -5139,119 +5218,54 @@
 💬 Lonely Girls Club Meet-up, Manchester — a solo-friendly night to make new friends, £8.95, 27 Oct.</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>本地生活类(集市/美食)</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J66" s="8" t="inlineStr">
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
-      <c r="K66" s="8" t="inlineStr">
+      <c r="K67" s="8" t="inlineStr">
         <is>
           <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
-      <c r="L66" s="8" t="inlineStr">
+      <c r="L67" s="8" t="inlineStr">
         <is>
           <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
-      <c r="M66" s="8" t="inlineStr">
+      <c r="M67" s="8" t="inlineStr">
         <is>
           <t>UK Food Lovers</t>
-        </is>
-      </c>
-      <c r="N66" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O66" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(烟花)</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
-        </is>
-      </c>
-      <c r="M67" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
@@ -5271,12 +5285,12 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
+          <t>Manchester 市政免费烟花夜（Platt Fields / Heaton Park / Wythenshawe Park）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
+          <t>Platt Fields Park, Wilmslow Road, Fallowfield, Manchester M14 6LA（另有 Heaton Park、Wythenshawe Park 两个点）</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -5286,12 +5300,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）20:00–04:00</t>
+          <t>7 Nov 2026（周六）17:00 低噪音场，20:00 主场烟花，之前有灯笼游行</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/House)</t>
+          <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
@@ -5301,17 +5315,17 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
+          <t>Manchester 市议会官方公布：市政烟花 2019 年后首次恢复；三个公园同时办</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
+          <t>https://www.manchester.gov.uk/news-stories/2026/free-fireworks-night-events-to-make-spectacular-return-in-manchester</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
+          <t>完全免费；Platt Fields 就在 Fallowfield 学生区，UoM 学生走路就到</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
@@ -5336,12 +5350,12 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>The Warehouse Project 万圣节场：NeXup（Luke Dean、Omar+、Locky 等）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Depot Mayfield, 11 Baring Street, Manchester M1 2PY</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -5351,37 +5365,37 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>31 Oct 2026（周六）20:00–04:00</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
+          <t>年轻人娱乐(Club/House)</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>WHP 是 Manchester 办了 20 年的旗舰俱乐部季，场地可容纳 10,000 人；这场在 Ticketmaster 和官网正规售票</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://thewarehouseproject.com/calendar/ ; https://www.skiddle.com/news/all/The-Warehouse-Project-2026-everything-you-need-to-know/61707/</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>万圣节夜 Manchester 最有代表性的 club 活动；⚠️WHP 票价通常不低，限 18 岁以上</t>
         </is>
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>Girls' Corner；Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
@@ -5401,52 +5415,52 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>社交类(女性) + 兴趣类(手工)</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
+          <t>电影/媒体 + 社交类(女性)</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>Girls' Corner</t>
+          <t>Girls' Corner；Reel Talk Club</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
@@ -5466,77 +5480,142 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
+          <t>Girl Gang MCR：Season of the Witch 系列活动</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Manchester 多个场地</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>city_only</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>社交类(女性) + 兴趣类(手工)</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Manchester's Finest 收录；系列里有 Craft &amp; Coven 手工夜、Pendle 女巫审判主题徒步等；没有单场售票数据</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>https://www.manchestersfinest.com/events/girl-gang-mcr-season-of-the-witch/ ; https://girlgangmcr.com/upcoming-events/</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>窗口内有多场可选；Pendle 徒步的具体日期没搜到，推之前要看官网确认单场日期</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="inlineStr">
+        <is>
+          <t>Girls' Corner</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
           <t>Lonely Girls Club Manchester 活动（10/27 场）</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Manchester（场地待公布）</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>27 Oct 2026（周二）</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>社交类(女性交友)</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J71" s="8" t="inlineStr">
+      <c r="J72" s="8" t="inlineStr">
         <is>
           <t>成熟的女性交友组织（有 Wikipedia 词条），London+Manchester 成员约 5.5 万（这是社群规模，不代表到场人数）；这场的具体内容官网写"即将公布"</t>
         </is>
       </c>
-      <c r="K71" s="8" t="inlineStr">
+      <c r="K72" s="8" t="inlineStr">
         <is>
           <t>https://www.llgc.co.uk/collections/manchester</t>
         </is>
       </c>
-      <c r="L71" s="8" t="inlineStr">
+      <c r="L72" s="8" t="inlineStr">
         <is>
           <t>票价 £8.95，便宜，专为一个人来交朋友设计；活动内容没公布，推之前再看一眼</t>
         </is>
       </c>
-      <c r="M71" s="8" t="inlineStr">
+      <c r="M72" s="8" t="inlineStr">
         <is>
           <t>Girls' Corner</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr">
+      <c r="N72" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O72" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>待制作：Newcastle university.png</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: NEWCASTLE 👇
@@ -5546,119 +5625,54 @@
 🎤 Reverend and The Makers, Northumbria SU — a big indie gig right on campus, 14 Nov.</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J72" s="8" t="inlineStr">
+      <c r="J73" s="8" t="inlineStr">
         <is>
           <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
-      <c r="K72" s="8" t="inlineStr">
+      <c r="K73" s="8" t="inlineStr">
         <is>
           <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
-      <c r="L72" s="8" t="inlineStr">
+      <c r="L73" s="8" t="inlineStr">
         <is>
           <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
-      <c r="M72" s="8" t="inlineStr">
+      <c r="M73" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
-        </is>
-      </c>
-      <c r="N72" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O72" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="inlineStr">
-        <is>
-          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
-        </is>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
-        </is>
-      </c>
-      <c r="M73" s="8" t="inlineStr">
-        <is>
-          <t>Durham university</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
@@ -5678,12 +5692,12 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+          <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -5693,37 +5707,37 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+          <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛马)</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+          <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+          <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+          <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Durham university</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
@@ -5743,77 +5757,142 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="5" t="inlineStr">
         <is>
+          <t>Newcastle Racecourse Bonfire Night（夜场赛马 + 烟花）</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Newcastle Racecourse, High Gosforth Park, Newcastle upon Tyne NE3 5HP</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>6 Nov 2026（周五）18:00 开门，约 20:30 放烟花</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(烟花/赛马)</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>赛马场官方年年举办，号称"本地区最大的烟花"（主办方说法）；已开售</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>https://www.newcastle-racecourse.co.uk/popular-events/fireworks</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>早鸟票成人 £9，很便宜；赛马 + 游乐场 + 烟花，一晚玩全套</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
           <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J75" s="8" t="inlineStr">
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
-      <c r="K75" s="8" t="inlineStr">
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
-      <c r="L75" s="8" t="inlineStr">
+      <c r="L76" s="8" t="inlineStr">
         <is>
           <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
-      <c r="M75" s="8" t="inlineStr">
+      <c r="M76" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr">
+      <c r="N76" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O76" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Durham university</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>待制作：Durham university.png</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: DURHAM 👇
@@ -5821,144 +5900,144 @@
 🎷 Durham Jazz Festival, Durham — from pop-up bar gigs to theatre headliners, 23–25 Oct.</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Beamish Halloween Evenings："The Un-living Museum of the North"</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>⚠️整季场次说法不一；官网确认有 28 Oct 2026 这一场，其余场次看官网</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(沉浸式/万圣节) + 一日游</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J76" s="8" t="inlineStr">
+      <c r="J77" s="8" t="inlineStr">
         <is>
           <t>英国知名露天博物馆的年度万圣节夜场；只能网上提前买票，往年经常售罄</t>
         </is>
       </c>
-      <c r="K76" s="8" t="inlineStr">
+      <c r="K77" s="8" t="inlineStr">
         <is>
           <t>https://www.beamish.org.uk/events/halloween-evening-28-oct-2026/ ; https://www.beamish.org.uk/halloween-at-beamish/</t>
         </is>
       </c>
-      <c r="L76" s="8" t="inlineStr">
+      <c r="L77" s="8" t="inlineStr">
         <is>
           <t>在纽卡斯尔和杜伦中间，两边都能去；有吓人路线，也有不吓人的；年卡在夜场不能用</t>
         </is>
       </c>
-      <c r="M76" s="8" t="inlineStr">
+      <c r="M77" s="8" t="inlineStr">
         <is>
           <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr">
+      <c r="N77" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O77" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Durham Jazz Festival 2026</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>23–25 Oct 2026</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/爵士)</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J77" s="8" t="inlineStr">
+      <c r="J78" s="8" t="inlineStr">
         <is>
           <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
         </is>
       </c>
-      <c r="K77" s="8" t="inlineStr">
+      <c r="K78" s="8" t="inlineStr">
         <is>
           <t>https://durhamjazzfestival.co.uk/ ; https://ukjazznews.com/durham-jazz-festival-2026-23-to-26-october/</t>
         </is>
       </c>
-      <c r="L77" s="8" t="inlineStr">
+      <c r="L78" s="8" t="inlineStr">
         <is>
           <t>场地都在杜伦市中心，有酒吧快闪演出，也有剧院大场，门槛可高可低</t>
         </is>
       </c>
-      <c r="M77" s="8" t="inlineStr">
+      <c r="M78" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr">
+      <c r="N78" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O78" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Leeds Uni Student Hub / Leeds University group 2</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>待制作：Leeds Uni Student Hub.png</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: LEEDS 👇
@@ -5967,119 +6046,54 @@
 🎸 Embrace 30th Anniversary Tour, O2 Academy Leeds — Britpop classics live, 13 Nov.</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Light Night Leeds 2026（主题：A City Speaks）</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Leeds city centre（40 多处装置，Briggate 等）</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>本地生活类(灯光艺术节)</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J78" s="8" t="inlineStr">
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>Leeds 市议会官方确认；号称英国最大的年度灯光艺术节；今年是 Leeds 400 周年的一部分；Yorkshire Evening Post 多次报道</t>
         </is>
       </c>
-      <c r="K78" s="8" t="inlineStr">
+      <c r="K79" s="8" t="inlineStr">
         <is>
           <t>https://news.leeds.gov.uk/news/return-of-citys-light-night-will-be-talk-of-the-town-as-it-moves-into-half-term ; https://www.yorkshireeveningpost.co.uk/whats-on/light-night-leeds-2026-briggate-projection-british-library-october-9208998</t>
         </is>
       </c>
-      <c r="L78" s="8" t="inlineStr">
+      <c r="L79" s="8" t="inlineStr">
         <is>
           <t>全部免费，40 多个互动装置遍布市中心，下课后顺路就能逛</t>
         </is>
       </c>
-      <c r="M78" s="8" t="inlineStr">
+      <c r="M79" s="8" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O78" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="7" t="n"/>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Leeds International Film Festival（第 40 届）</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>电影/媒体</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
-        </is>
-      </c>
-      <c r="K79" s="8" t="inlineStr">
-        <is>
-          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
-        </is>
-      </c>
-      <c r="M79" s="8" t="inlineStr">
-        <is>
-          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
@@ -6099,77 +6113,142 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="5" t="inlineStr">
         <is>
+          <t>Leeds International Film Festival（第 40 届）</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>Reel Talk Club</t>
+        </is>
+      </c>
+      <c r="N80" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O80" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
           <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J80" s="8" t="inlineStr">
+      <c r="J81" s="8" t="inlineStr">
         <is>
           <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
-      <c r="K80" s="8" t="inlineStr">
+      <c r="K81" s="8" t="inlineStr">
         <is>
           <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
-      <c r="L80" s="8" t="inlineStr">
+      <c r="L81" s="8" t="inlineStr">
         <is>
           <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
-      <c r="M80" s="8" t="inlineStr">
+      <c r="M81" s="8" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
         </is>
       </c>
-      <c r="N80" s="8" t="inlineStr">
+      <c r="N81" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O81" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Huddersfield Uni Student Hub</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>待制作：Huddersfield Uni Student Hub.png</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: BONFIRE NIGHT 👇
@@ -6177,144 +6256,144 @@
 🎆 Mirfield Bonfire &amp; Firework Extravaganza, Mirfield — bonfire, music stage and funfair, 7 Nov.</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Huddersfield &amp; District Round Table 慈善篝火烟花夜</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>7 Nov 2026（周六）17:00 开门</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>Yorkshire Live 列入约克郡篝火夜推荐；本地慈善机构年年办；没有售票数据</t>
         </is>
       </c>
-      <c r="K81" s="8" t="inlineStr">
+      <c r="K82" s="8" t="inlineStr">
         <is>
           <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
         </is>
       </c>
-      <c r="L81" s="8" t="inlineStr">
+      <c r="L82" s="8" t="inlineStr">
         <is>
           <t>成人 £5，很便宜，离市中心近</t>
         </is>
       </c>
-      <c r="M81" s="8" t="inlineStr">
+      <c r="M82" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N81" s="8" t="inlineStr">
+      <c r="N82" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O82" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="n"/>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="5" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Mirfield Bonfire &amp; Firework Extravaganza</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>Mirfield Showground, Mirfield, West Yorkshire</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>7 Nov 2026（周六）16:00 开门，约 19:30 放烟花</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J82" s="8" t="inlineStr">
+      <c r="J83" s="8" t="inlineStr">
         <is>
           <t>Yorkshire Live 列入约克郡最大篝火夜之一；有音乐舞台和游乐场；没有售票数据</t>
         </is>
       </c>
-      <c r="K82" s="8" t="inlineStr">
+      <c r="K83" s="8" t="inlineStr">
         <is>
           <t>https://www.examinerlive.co.uk/whats-on/family-kids-news/bonfire-night-2026-yorkshires-biggest-34659274</t>
         </is>
       </c>
-      <c r="L82" s="8" t="inlineStr">
+      <c r="L83" s="8" t="inlineStr">
         <is>
           <t>离 Huddersfield 约 10 公里，比市内的活动规模大</t>
         </is>
       </c>
-      <c r="M82" s="8" t="inlineStr">
+      <c r="M83" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N82" s="8" t="inlineStr">
+      <c r="N83" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O83" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Staffs Student Life | Stoke / Keele Campus Life</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>待制作：Staffs Student Life | Stoke.png</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: STOKE 👇
@@ -6323,114 +6402,49 @@
 👻 Big Halloween Street Party, Hanley — free street party in the city centre, 31 Oct.</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Trentham Halloween Festival</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>Trentham Estate, Stone Road, Trentham, Stoke-on-Trent ST4 8JG</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>31 Oct – 1 Nov 2026</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(万圣节/户外)</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J83" s="8" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>Trentham Estate 官方主办，Visit Staffordshire 收录；有火舞表演、南瓜灯小路、静音 disco</t>
         </is>
       </c>
-      <c r="K83" s="8" t="inlineStr">
+      <c r="K84" s="8" t="inlineStr">
         <is>
           <t>https://trentham.co.uk/events/trentham-halloween-festival/ ; https://www.visitstaffordshire.com/event/trentham-halloween-festival/234108101/</t>
         </is>
       </c>
-      <c r="L83" s="8" t="inlineStr">
+      <c r="L84" s="8" t="inlineStr">
         <is>
           <t>离 Keele、Staffs 都近；静音 disco 和火舞适合年轻人</t>
-        </is>
-      </c>
-      <c r="M83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n"/>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="7" t="n"/>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Stoke-on-Trent Comedy Festival（含 Adam Kay、Hannah Byczkowski）</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>King's Hall, Glebe Street, Stoke-on-Trent ST4 1HH</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>13–15 Nov 2026（Adam Kay：14 Nov 20:00）</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(喜剧)</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>市政场馆 King's Hall 主办的喜剧节；Adam Kay（This Is Going to Hurt）是知名巡演喜剧人</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>https://www.stoke.gov.uk/kingshallevents ; https://www.songkick.com/metro-areas/24537-uk-stoke-on-trent/november-2026</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr">
-        <is>
-          <t>周末喜剧节，有好几场可以选；Byczkowski 是《The Traitors》第一季冠军，话题度高</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
@@ -6455,77 +6469,142 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="5" t="inlineStr">
         <is>
+          <t>Stoke-on-Trent Comedy Festival（含 Adam Kay、Hannah Byczkowski）</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>King's Hall, Glebe Street, Stoke-on-Trent ST4 1HH</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>13–15 Nov 2026（Adam Kay：14 Nov 20:00）</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>市政场馆 King's Hall 主办的喜剧节；Adam Kay（This Is Going to Hurt）是知名巡演喜剧人</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>https://www.stoke.gov.uk/kingshallevents ; https://www.songkick.com/metro-areas/24537-uk-stoke-on-trent/november-2026</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>周末喜剧节，有好几场可以选；Byczkowski 是《The Traitors》第一季冠军，话题度高</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
           <t>Big Halloween Street Party（免费）</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>Stoke-on-Trent City Centre（Hanley）</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026（周六）10:00 起</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>本地生活类(万圣节街头活动)</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J85" s="8" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>Visit Stoke 官方收录，年年举办的免费街头活动；偏家庭向</t>
         </is>
       </c>
-      <c r="K85" s="8" t="inlineStr">
+      <c r="K86" s="8" t="inlineStr">
         <is>
           <t>https://www.visitstoke.co.uk/whats-on/the-big-halloween-street-party-p2022331</t>
         </is>
       </c>
-      <c r="L85" s="8" t="inlineStr">
+      <c r="L86" s="8" t="inlineStr">
         <is>
           <t>免费，Staffs 在 Hanley 附近；有街头表演和手工市集</t>
         </is>
       </c>
-      <c r="M85" s="8" t="inlineStr">
+      <c r="M86" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N85" s="8" t="inlineStr">
+      <c r="N86" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O86" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>University of Cardiff / Cardiff Metropolitan University</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>待制作：University of Cardiff.png</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: CARDIFF 👇
@@ -6537,114 +6616,49 @@
 🏳️‍🌈 Iris Prize LGBTQ+ Film Festival, Cardiff — 20th anniversary &amp; awards night, to 18 Oct.</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Cardiff's Winter Wonderland 2026（冰场 / 摩天轮 / 冰壶）</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Cardiff Castle, Castle Street, Cardiff CF10 3RB &amp; City Hall Lawn</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(滑冰/游乐)</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
+      <c r="I87" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J86" s="8" t="inlineStr">
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>Visit Cardiff 官方收录，年年举办；Nation.Cymru、Wales247 报道了 2026 年日期</t>
         </is>
       </c>
-      <c r="K86" s="8" t="inlineStr">
+      <c r="K87" s="8" t="inlineStr">
         <is>
           <t>https://www.visitcardiff.com/christmas/cardiffs-winter-wonderland/ ; https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
         </is>
       </c>
-      <c r="L86" s="8" t="inlineStr">
+      <c r="L87" s="8" t="inlineStr">
         <is>
           <t>城堡里的露天冰场很出片；今年新增冰壶体验</t>
-        </is>
-      </c>
-      <c r="M86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N86" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O86" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="7" t="n"/>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>St Fagans Halloween Nights（每晚烧 Wicker Man）</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>St Fagans National Museum of History, Cardiff CF5 6XB</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>29–31 Oct 2026，17:30–21:00</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(沉浸式/万圣节) + 本地文化</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>威尔士国家博物馆主办；官方说"门票预计很快售罄"；年年举办</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr">
-        <is>
-          <t>https://museum.wales/stfagans/whatson/12647/Halloween-Nights/ ; https://letsgowiththechildren.co.uk/events/halloween-nights-2026-at-st-fagans-national-museum-of-history-cardiff</t>
-        </is>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
         </is>
       </c>
       <c r="M87" s="8" t="inlineStr">
@@ -6669,12 +6683,12 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>威尔士 vs 日本（Nations Championship 橄榄球）</t>
+          <t>St Fagans Halloween Nights（每晚烧 Wicker Man）</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
+          <t>St Fagans National Museum of History, Cardiff CF5 6XB</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -6684,12 +6698,12 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）16:40 开球</t>
+          <t>29–31 Oct 2026，17:30–21:00</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>运动户外(观赛)</t>
+          <t>年轻人娱乐(沉浸式/万圣节) + 本地文化</t>
         </is>
       </c>
       <c r="I88" s="9" t="inlineStr">
@@ -6699,17 +6713,17 @@
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>WRU 官方公布；球场官网有单场售票页</t>
+          <t>威尔士国家博物馆主办；官方说"门票预计很快售罄"；年年举办</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>https://www.wru.wales/2026/03/dates-confirmed-for-wales-home-nations-championship-fixtures ; https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-japan/</t>
+          <t>https://museum.wales/stfagans/whatson/12647/Halloween-Nights/ ; https://letsgowiththechildren.co.uk/events/halloween-nights-2026-at-st-fagans-national-museum-of-history-cardiff</t>
         </is>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
-          <t>市中心球场，比赛日全城都是气氛；对日本这场的票通常比对新西兰便宜</t>
+          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr">
@@ -6734,7 +6748,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>威尔士 vs 新西兰（Nations Championship 橄榄球）</t>
+          <t>威尔士 vs 日本（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -6749,7 +6763,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）</t>
+          <t>7 Nov 2026（周六）16:40 开球</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -6764,17 +6778,17 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>WRU 官方公布；对全黑队是秋季重头戏</t>
+          <t>WRU 官方公布；球场官网有单场售票页</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-new-zealand/</t>
+          <t>https://www.wru.wales/2026/03/dates-confirmed-for-wales-home-nations-championship-fixtures ; https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-japan/</t>
         </is>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
-          <t>⚠️对全黑队的票最贵；买不到票也可以去市中心酒吧看直播</t>
+          <t>市中心球场，比赛日全城都是气氛；对日本这场的票通常比对新西兰便宜</t>
         </is>
       </c>
       <c r="M89" s="8" t="inlineStr">
@@ -6799,47 +6813,47 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Cardiff Christmas Market 2026（附 Queen Street 维多利亚圣诞市集）</t>
+          <t>威尔士 vs 新西兰（Nations Championship 橄榄球）</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>St John Street / Working Street / Trinity Street / Hills Street / The Hayes, Cardiff city centre（维多利亚市集在 Queen Street）</t>
+          <t>Principality Stadium, Westgate Street, Cardiff CF10 1NS</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>12 Nov – 23 Dec 2026（维多利亚市集只在 12–15 Nov）</t>
+          <t>14 Nov 2026（周六）</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>本地生活类(集市/美食)</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
+          <t>运动户外(观赛)</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>年年举办的市中心圣诞市集；维多利亚市集是 2026 年新增的</t>
+          <t>WRU 官方公布；对全黑队是秋季重头戏</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+          <t>https://www.principalitystadium.wales/event/nations-championship-2026-wales-v-new-zealand/</t>
         </is>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
-          <t>免费逛；12–15 Nov 这几天两个市集同时开</t>
+          <t>⚠️对全黑队的票最贵；买不到票也可以去市中心酒吧看直播</t>
         </is>
       </c>
       <c r="M90" s="8" t="inlineStr">
@@ -6864,77 +6878,142 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
+          <t>Cardiff Christmas Market 2026（附 Queen Street 维多利亚圣诞市集）</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>St John Street / Working Street / Trinity Street / Hills Street / The Hayes, Cardiff city centre（维多利亚市集在 Queen Street）</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>12 Nov – 23 Dec 2026（维多利亚市集只在 12–15 Nov）</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/美食)</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>年年举办的市中心圣诞市集；维多利亚市集是 2026 年新增的</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wales247.co.uk/cardiff-confirms-christmas-lights-date-and-festive-attractions-for-2026</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>免费逛；12–15 Nov 这几天两个市集同时开</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
           <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>Cardiff（多个场地）</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>city_only</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>电影/媒体</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J91" s="8" t="inlineStr">
+      <c r="J92" s="8" t="inlineStr">
         <is>
           <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
         </is>
       </c>
-      <c r="K91" s="8" t="inlineStr">
+      <c r="K92" s="8" t="inlineStr">
         <is>
           <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
         </is>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L92" s="8" t="inlineStr">
         <is>
           <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
         </is>
       </c>
-      <c r="M91" s="8" t="inlineStr">
+      <c r="M92" s="8" t="inlineStr">
         <is>
           <t>Reel Talk Club</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr">
+      <c r="N92" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O92" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>University of Aberdeen Freshers 2026</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>待制作：University of Aberdeen Freshers 2026.png</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: ABERDEEN 👇
@@ -6943,114 +7022,49 @@
 🎆 Aberdeen Fireworks Night, Aberdeen Beach — the council's free display (2026 details TBC), 5 Nov.</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>soundfestival 2026（新音乐节）</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>The Lemon Tree / Cowdray Hall / King's Pavilion 等，Aberdeen &amp; Aberdeenshire</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>22–31 Oct 2026</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(Live Music/实验音乐)</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J92" s="8" t="inlineStr">
+      <c r="J93" s="8" t="inlineStr">
         <is>
           <t>Creative Scotland 官方报道 2026 年节目；欧洲知名的新音乐节，年年举办；有一场在前核掩体里</t>
         </is>
       </c>
-      <c r="K92" s="8" t="inlineStr">
+      <c r="K93" s="8" t="inlineStr">
         <is>
           <t>https://www.creativescotland.com/news-stories/latest-news/archive/2026/08/acclaimed-new-music-festival-reveals-details-of-2026-edition ; https://sound-scotland.co.uk/</t>
         </is>
       </c>
-      <c r="L92" s="8" t="inlineStr">
+      <c r="L93" s="8" t="inlineStr">
         <is>
           <t>街头表演、声音漫步、装置艺术，形式新鲜，很多场免费或便宜</t>
-        </is>
-      </c>
-      <c r="M92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O92" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Aberdeen Christmas Village 2026</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Broad Street, Aberdeen city centre</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>本地生活类(集市/节庆)</t>
-        </is>
-      </c>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>Aberdeen 市议会、Aberdeen Inspired 主办，年年举办</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>https://www.aberdeeninspired.com/festival/aberdeen-christmas-market/christmas-village ; https://www.aberdeencity.gov.uk/news/christmas-village-launches-citys-festive-celebrations</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>市中心免费逛，开幕那周就能去</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr">
@@ -7075,142 +7089,207 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
+          <t>Aberdeen Christmas Village 2026</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Broad Street, Aberdeen city centre</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>12 Nov 2026 – 3 Jan 2027（窗口内为 12–15 Nov）</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/节庆)</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>Aberdeen 市议会、Aberdeen Inspired 主办，年年举办</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>https://www.aberdeeninspired.com/festival/aberdeen-christmas-market/christmas-village ; https://www.aberdeencity.gov.uk/news/christmas-village-launches-citys-festive-celebrations</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>市中心免费逛，开幕那周就能去</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
           <t>Aberdeen Fireworks Night（市议会主办）</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>Aberdeen Beach / Beach Boulevard 一带（往年因海滩施工改在 North Pier 燃放）</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>⚠️每年固定 5 Nov（2026 年是周四）19:30；2026 年的官方公告还没看到</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(烟花)</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr">
         <is>
           <t>中热度</t>
         </is>
       </c>
-      <c r="J94" s="8" t="inlineStr">
+      <c r="J95" s="8" t="inlineStr">
         <is>
           <t>Aberdeen 市议会年年主办的免费烟花；Press and Journal 每年都有报道</t>
         </is>
       </c>
-      <c r="K94" s="8" t="inlineStr">
+      <c r="K95" s="8" t="inlineStr">
         <is>
           <t>https://www.aberdeencity.gov.uk/node/8869 ; https://www.pressandjournal.co.uk/fp/news/6869573/all-you-need-to-know-aberdeen-fireworks-2025/</t>
         </is>
       </c>
-      <c r="L94" s="8" t="inlineStr">
+      <c r="L95" s="8" t="inlineStr">
         <is>
           <t>免费；推之前确认一下 2026 年的官方公告和燃放地点</t>
         </is>
       </c>
-      <c r="M94" s="8" t="inlineStr">
+      <c r="M95" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N94" s="8" t="inlineStr">
+      <c r="N95" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O95" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O94"/>
+  <autoFilter ref="A1:O95"/>
   <mergeCells count="75">
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B53:B55"/>
     <mergeCell ref="A21:A25"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B66:B71"/>
+    <mergeCell ref="A57:A59"/>
     <mergeCell ref="C21:C25"/>
-    <mergeCell ref="C86:C91"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C73:C76"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C45:C46"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A67:A72"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B82:B83"/>
     <mergeCell ref="B10:B18"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="B86:B91"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="B73:B76"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A79:A81"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A42:A44"/>
     <mergeCell ref="A10:A18"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B30:B36"/>
-    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="A86:A91"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="B67:B72"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B31:B37"/>
     <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C30:C36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C67:C72"/>
+    <mergeCell ref="C93:C95"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="C66:C71"/>
+    <mergeCell ref="B57:B59"/>
     <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="C47:C49"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C87:C92"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A73:A76"/>
     <mergeCell ref="C10:C18"/>
-    <mergeCell ref="A56:A58"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7452,7 +7531,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>英国线下 CS2 基本只有 EPIC.LAN；NSE 大学联赛以线上为主，官网被拦，赛程没拿到；未达 3–5 条</t>
+          <t>英国线下 CS2 基本只有 EPIC49；NSE 大学联赛以线上为主，官网被拦，赛程没拿到；未达 3–5 条</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7903,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>第1轮 已搜/有结果（弱）</t>
+          <t>第1轮 已搜/有结果</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -7832,7 +7911,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>EPIC.LAN 有没有 Valorant 赛还没确认；Champions 总决赛（10/18，上海）没搜到英国线下观赛点；未达 3–5 条</t>
+          <t>EPIC49 有 VALORANT 锦标赛（赛事列表已确认）；Champions 总决赛（10/18，上海）没搜到英国线下观赛点；未达 3–5 条</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9110,12 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>信息不全</t>
+          <t>已更正</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>EPIC.LAN：届数有的写 EPIC48 有的写 EPIC49；有没有 Valorant 赛、入场票价都没核实</t>
+          <t>EPIC.LAN：之前写的"EPIC48 CS2 30 Oct–1 Nov"不对，EPIC48 其实在 7 月（16–19 Jul，已结束）；10/29–11/1 这届是 EPIC49，有 CS2 和 VALORANT 两项比赛。入场票价没核实</t>
         </is>
       </c>
     </row>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Track B 30天活动'!$A$1:$O$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'社群覆盖清单'!$A$1:$E$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核实与缺口'!$A$1:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核实与缺口'!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1201,11 +1201,10 @@
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: MUSIC 👇
-🎆 Ally Pally Fireworks &amp; Drone Festival, London — fireworks, drones and an Eats Everything DJ set, 7–8 Nov.
-🎇 Battersea Park Fireworks, London — fireworks plus a Rudimental DJ set, 7–8 Nov.
 🎃 Skindred Halloween Special, Alexandra Palace — with Alien Ant Farm, Spineshank &amp; Orgy, 31 Oct.
 🎧 Ben Hemsley Halloween Day Rave, Gateshead Stadium — house &amp; trance all day, 2,400+ going (18+), 31 Oct.
-🤘 Core. Festival, Glasgow — heavy music weekend incl. Skindred at the Barrowland, 13–15 Nov.
+🤘 Core. Festival, Glasgow — a heavy-music weekend with Pig Destroyer, Eyehategod &amp; more, 13–15 Nov.
+🎸 Skindred, Barrowland Ballroom, Glasgow — the "You Got This" tour hits a legendary venue, 13 Nov.
 🎸 Pop Mutations x Tiny Changes, Glasgow — an indie weekender across four grassroots venues, 13–14 Nov.
 🤘 Skindred, O2 Academy Birmingham — a rock night on Halloween eve, 30 Oct.
 🎤 Reverend and The Makers, Northumbria SU — a big indie gig right on campus, 14 Nov.
@@ -1214,7 +1213,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1229,12 +1228,12 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -1244,17 +1243,17 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1279,12 +1278,12 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1294,12 +1293,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>年轻人娱乐(Club/电子)</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1309,22 +1308,22 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London；St Mary's University, Twickenham</t>
+          <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
@@ -1344,52 +1343,52 @@
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
+          <t>Core. 重型音乐节（Pig Destroyer / Eyehategod / Wormrot / Raging Speedhorn 等）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Glasgow 多个场地（具体场地看官网和 What's On Glasgow）</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:30</t>
+          <t>13–15 Nov 2026</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
+          <t>What's On Glasgow 收录，号称"苏格兰最新的重型音乐节"，今年第二届；阵容里有 Pig Destroyer、Eyehategod 等国际乐队</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://corepresents.seetickets.com/search/all</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
+          <t>金属、硬核爱好者的周末；多个场馆可以串场</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
+          <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
@@ -1409,12 +1408,12 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Ben Hemsley 万圣节日场 Rave（with Ewan McVicar）</t>
+          <t>Skindred "You Got This" 巡演 格拉斯哥站</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Gateshead International Stadium, Neilson Road, Gateshead NE10 0EF</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1424,37 +1423,37 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）13:30–23:00，16:00 后停止入场</t>
+          <t>13 Nov 2026（周五）19:00 开门</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Club/电子)</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Skiddle 显示"hot seller"、2,448+ 人标记参加（平台实时数字）；机库场地可容纳 6,000 人</t>
+          <t>全英巡演的格拉斯哥站，Visit Glasgow 有收录；和 Core. 音乐节同一个周末，但不属于 Core. 阵容</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>https://www.skiddle.com/whats-on/Gateshead/Gateshead-Stadium/ ; https://www.skiddle.com/artists/Ben-Hemsley-123570182/</t>
+          <t>https://www.visitglasgow.com/events/skindred-13112026-139289 ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>万圣节当天东北部最大的 house / trance 活动之一；限 18 岁以上；地铁可直达</t>
+          <t>Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
+          <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
@@ -1474,12 +1473,12 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1489,12 +1488,12 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>13–14 Nov 2026</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(Live Music/独立音乐)</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1504,17 +1503,17 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1539,27 +1538,27 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Pop Mutations x Tiny Changes 小型音乐周末</t>
+          <t>Skindred "You Got This" 巡演 伯明翰站</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>13–14 Nov 2026</t>
+          <t>30 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立音乐)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1569,22 +1568,22 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>Clash 杂志、VisitScotland 报道；阵容有 Kathryn Joseph、Rozi Plain、The Pastels、Billy Nomates；和心理健康慈善机构 Tiny Changes 合办</t>
+          <t>NME、Kerrang! 报道的全英巡演；See Tickets、Live Nation 正规售票；嘉宾 Alien Ant Farm、Spineshank</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>https://www.clashmusic.com/live/pop-mutations-x-tiny-changes-confirm-intimate-glasgow-weekender ; https://www.popmutations.com/events/pop-mutations-x-tiny-changes</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/o2-academy-birmingham/3619857 ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>独立、小众音乐爱好者的首选，都在市中心小场馆，氛围好，票价通常不高</t>
+          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
+          <t>BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
@@ -1604,12 +1603,12 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Skindred "You Got This" 巡演 伯明翰站</t>
+          <t>Reverend and The Makers 演唱会</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>O2 Academy Birmingham, 16–18 Horsefair, Bristol Street, Birmingham B1 1DB</t>
+          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1619,12 +1618,12 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>30 Oct 2026（周五）</t>
+          <t>14 Nov 2026（周六）19:00 开门</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
+          <t>年轻人娱乐(Live Music/独立摇滚)</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1634,22 +1633,22 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>万圣节前夜的摇滚场，O2 Academy 就在市中心，BCU 和 SCCB 过去都方便</t>
+          <t>就在 Northumbria 学生会里，在校生走路就到</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
+          <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
@@ -1669,12 +1668,12 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Reverend and The Makers 演唱会</t>
+          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Northumbria Students' Union, 2 Sandyford Road, Newcastle upon Tyne NE1 8SB</t>
+          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1684,12 +1683,12 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）19:00 开门</t>
+          <t>13 Nov 2026（周五）19:00</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/独立摇滚)</t>
+          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1699,22 +1698,22 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>SJM Concerts 主办，Ticketmaster / Songkick / Bandsintown 都有正式票务页；成熟乐队巡演</t>
+          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>https://www.songkick.com/concerts/43167629-reverend-and-the-makers-at-northumbria-students-union ; https://www.ents24.com/newcastle-upon-tyne-events/northumbria-university-students-union/reverend-and-the-makers/7473947</t>
+          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>就在 Northumbria 学生会里，在校生走路就到</t>
+          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
+          <t>Leeds Uni Student Hub / Leeds University group 2</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
@@ -1729,82 +1728,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Embrace 30 周年巡演（嘉宾：The Rolling People / The Bunny Suit）</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>O2 Academy Leeds, 55 Cookridge Street, Leeds LS2 3AW</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>13 Nov 2026（周五）19:00</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(Live Music/英伦摇滚)</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Live Nation / Academy Music Group 正式售票；乐队 30 周年新专辑巡演</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>https://www.academymusicgroup.com/o2academyleeds/events/embrace-tickets-ae136632 ; https://www.gigsandtours.com/event/embrace/o2-academy-leeds/3605026</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>票价约 £37.70；场馆离 Leeds 大学、Leeds Beckett 都近</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>Leeds Uni Student Hub / Leeds University group 2</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Page Turners Club</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>待制作：Page Turners Club.png</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: BOOKS &amp; STORIES 👇
@@ -1812,29 +1746,94 @@
 📚 Off the Shelf Festival of Words, Sheffield — talks, readings and screenings, to 25 Oct.</t>
         </is>
       </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>21–31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>兴趣类(文学/讲故事)</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Scottish International Storytelling Festival 2026（主题：Bird &amp; Beast）</t>
+          <t>Off the Shelf Festival of Words 2026</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Scottish Storytelling Centre, 43–45 High Street, Edinburgh EH1 1SR（主场馆 Netherbow Theatre）</t>
+          <t>Sheffield（市内多个场地）</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>21–31 Oct 2026</t>
+          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>兴趣类(文学/讲故事)</t>
+          <t>兴趣类(文学/讲座)</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -1844,22 +1843,22 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>年年举办的国际讲故事节，Edinburgh Festival City 和 Forever Edinburgh 官方都有收录；合作场地有 Royal Botanic Garden、National Library of Scotland</t>
+          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>https://www.sisf.org.uk/ ; https://www.edinburghfestivalcity.com/festivals/scottish-international-storytelling-festival ; https://theqr.co.uk/2026/09/15/scottish-storytelling-festival-2026-returns-with-bird-beast/</t>
+          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>文学、苏格兰文化爱好者会喜欢；在 Royal Mile 上，很多场次价格不高</t>
+          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
+          <t>Sheffield Hallam University / University of Sheffield</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
@@ -1874,82 +1873,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Off the Shelf Festival of Words 2026</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Sheffield（市内多个场地）</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>city_only</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>9–25 Oct 2026（窗口内为 15–25 Oct）</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>兴趣类(文学/讲座)</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>谢菲尔德官方旅游网站列为"headline event"；年年举办的大型文学节，有数百场活动</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>https://www.welcometosheffield.co.uk/content/events/off-the-shelf-festival-of-words-2026/</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>有讲座、朗读、放映，很多场次免费或便宜；由谢菲尔德大学参与主办</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>Sheffield Hallam University / University of Sheffield</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Reel Talk Club</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>待制作：Reel Talk Club.png</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: FILM 👇
@@ -1960,24 +1894,89 @@
 🎞️ Edinburgh Short Film Festival, Edinburgh — bite-size screenings for film lovers, 6–22 Nov.</t>
         </is>
       </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>电影/媒体</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="n"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>Leeds International Film Festival（第 40 届）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1992,22 +1991,22 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
+          <t>Leeds Uni Student Hub / Leeds University group 2</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
@@ -2027,52 +2026,52 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Leeds International Film Festival（第 40 届）</t>
+          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House, 73 Brudenell Road, Leeds LS6 1JD / Everyman Leeds 等多个影院</t>
+          <t>Islington Mill, James Street, Salford</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>29 Oct – 15 Nov 2026（有来源写 5–22 Nov；主流来源和官方节目时间表都写 29 Oct 开始）</t>
+          <t>31 Oct 2026（周六）18:00–24:00</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
+          <t>电影/媒体 + 社交类(女性)</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>第 40 届，英国历史最悠久的电影节之一；10/1 节目上线、10/8 单片开票（YEP 报道）</t>
+          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>https://www.leedsfilm.com/liff-2026-6ftb ; https://www.yorkshireeveningpost.co.uk/whats-on/arts-and-entertainment/leeds-international-film-festival-2026-opening-films-liff-40th-9021020</t>
+          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>Hyde Park Picture House 就在 Leeds 大学学生区旁边；几乎整个窗口期都有放映</t>
+          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>Leeds Uni Student Hub / Leeds University group 2</t>
+          <t>Girls' Corner；The University of Manchester</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
@@ -2092,27 +2091,27 @@
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Girl Gang MCR：The Craft 30 周年沉浸式放映</t>
+          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Cardiff（多个场地）</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）18:00–24:00</t>
+          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>电影/媒体 + 社交类(女性)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2122,22 +2121,22 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>票务页显示"1/3 Sold"（真实售票信号）；主办方两次获 Film Society of the Year "Best Single Event"</t>
+          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>https://www.tickettailor.com/events/girlgangmcr/2344142 ; https://girlgangmcr.com/previous-projects/immersive-screenings/</t>
+          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>万圣节当晚的女巫主题放映，带 disco 和手工环节，女生结伴去很合适；注意 Girl Gang 受众年龄偏宽（16–80）</t>
+          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>Girls' Corner；The University of Manchester</t>
+          <t>University of Cardiff / Cardiff Metropolitan University</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
@@ -2157,12 +2156,12 @@
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Iris Prize LGBTQ+ Film Festival 20 周年</t>
+          <t>Edinburgh Short Film Festival（第 16 届）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Cardiff（多个场地）</t>
+          <t>Edinburgh（多个场地）</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2172,7 +2171,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>12–18 Oct 2026（窗口内为 15–18 Oct；18 Oct 颁奖）</t>
+          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2180,29 +2179,29 @@
           <t>电影/媒体</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>第 20 届，Visit Cardiff、Visit Wales 官方收录；Iris Prize 是有影响力的 LGBTQ+ 短片奖</t>
+          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>https://irisprize.org/ ; https://www.visitcardiff.com/events/iris-prize/</t>
+          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>窗口内有 Best British Day、20 周年庆典、颁奖夜；要推得早</t>
+          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>University of Cardiff / Cardiff Metropolitan University</t>
+          <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
@@ -2217,240 +2216,175 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Edinburgh Short Film Festival（第 16 届）</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Edinburgh（多个场地）</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>city_only</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>6–22 Nov 2026（窗口内为 6–15 Nov）</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>电影/媒体</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>已办到第 16 届，在 FilmFreeway / Festhome 正规征片；没搜到售票数据</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>https://filmfreeway.com/EdinburghShortFilmFestival ; https://www.awn.com/event/edinburgh-short-film-festival-2026</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>短片放映门槛低，适合电影爱好者和传媒专业学生；具体场地和场次要看官网</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Snack Finds &amp; Picks</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>待制作：Snack Finds &amp; Picks.png</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: FESTIVE FOOD MARKETS 👇
 🎄 Frankfurt Christmas Market, Birmingham — German food &amp; mulled wine by New Street, from 5 Nov.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Birmingham's Frankfurt Christmas Market 2026</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>本地生活类(集市/美食)</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UK Food Lovers；BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Swim Wave Tribe</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>待制作：Swim Wave Tribe.png</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: WILD SWIMMING 👇
 🏊 Capernwray Lake Swim, Carnforth — a late-season open-water swim (cold-water experience needed), 31 Oct.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Capernwray 湖泊公开水域游泳（Lake Swim）</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>31 Oct 2026</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>运动户外(游泳)</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>潜在价值</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>仅见于 Outdoor Swimmer 杂志活动日历；主办方未核实（疑为 T2 Events，他们在该场地办过比赛）；无报名数据</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>https://outdoorswimmer.com/events/ ; https://www.t2.events/our-events/capernwray-open-water-swim/</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>窗口内极少数的户外游泳活动，10 月底水温很低，只适合有冷水经验的人；离 Lancaster 大学约 10 公里</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>University of Lancaster</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>UK Food Lovers</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>待制作：UK Food Lovers.png</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: FESTIVE FOOD MARKETS 👇
@@ -2458,14 +2392,79 @@
 🎄 Manchester Christmas Markets, Manchester city centre — the markets are back, free to wander, from 6 Nov.</t>
         </is>
       </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>venue_only</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>本地生活类(集市/美食)</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>Snack Finds &amp; Picks；BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Birmingham's Frankfurt Christmas Market 2026</t>
+          <t>Manchester Christmas Markets 2026</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Victoria Square &amp; New Street（Corporation Street 至 Bullring 段）, Birmingham city centre</t>
+          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2475,7 +2474,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>5 Nov – 24 Dec 2026（窗口内为 5–15 Nov；8 Nov 纪念日星期天 13:00 开）</t>
+          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -2490,22 +2489,22 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>伯明翰市议会官方公布日期；年年举办，号称德国、奥地利以外最大的正宗德式圣诞市集（主办方说法）</t>
+          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>https://www.birmingham.gov.uk/news/article/1841/birminghams_frankfurt_christmas_market_dates_confirmed ; https://thebfcm.co.uk/ ; https://www.centralbid.co.uk/events/birminghams-frankfurt-christmas-market-2026/</t>
+          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>免费入场，就在 New Street 站旁，吃喝逛一站搞定</t>
+          <t>免费入场，市中心多个点位，逛吃一条龙</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Snack Finds &amp; Picks；BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
+          <t>The University of Manchester</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
@@ -2520,161 +2519,96 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Manchester Christmas Markets 2026</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Albert Square / Cathedral Gardens / Exchange Square 等，Manchester city centre</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>venue_only</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>6 Nov – 22 Dec 2026（Albert Square、Cathedral Gardens 开到 3 Jan 2027；窗口内为 6–15 Nov）</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>本地生活类(集市/美食)</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>年年举办的全英知名圣诞市集，The Manc 报道了 2026 年开市日期和新增点位</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>https://themanc.com/news/manchester-christmas-markets-2026-opening-date-announced-including-new-spots/ ; https://www.visitmanchester.com/whats-on/whats-on-this-christmas-in-manchester/</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>免费入场，市中心多个点位，逛吃一条龙</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>The University of Manchester</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Valorant Riot Crew</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>待制作：Valorant Riot Crew.png</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: VALORANT &amp; LAN 👇
 🎯 EPIC49 LAN, Kettering — 4 days of LAN with a VALORANT tournament (BYOC ticket needed), 29 Oct–1 Nov.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>EPIC49 LAN Party（含 CS2 / VALORANT / StarCraft II / osu! 锦标赛）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Kettering Leisure Village, Kettering, Northamptonshire</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>venue_only</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>29 Oct 16:00 – 1 Nov 16:00 2026（锦标赛在 30 Oct – 1 Nov）</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>年轻人娱乐(电竞/LAN)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>高热度</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>英国老牌 LAN 系列，已办到第 49 届，每年两届；这届 700 个电脑位；官网有 EPIC49 专页，赛事项目包括 CS2 和 VALORANT</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>https://www.epiclan.co.uk/epic49 ; https://www.yorkshirepudd.co.uk/epic49-kettering-lan/ ; https://esportsinsider.com/2025/07/epic-lan-unveils-dates-for-2026-events</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>自带电脑参加 4 天 LAN；报比赛必须买 BYOC 票，而且一张票只能报一个项目；万圣节夜有社区派对；票价没核实</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>The Gaming Corner；CS2 Frag Hub</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>待制作：UCL Hub.png</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: LONDON &amp; CAMPUS 👇
@@ -2687,14 +2621,79 @@
 🎃 Skindred Halloween Special, Alexandra Palace — with Alien Ant Farm, Spineshank &amp; Orgy, 31 Oct.</t>
         </is>
       </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>MCM Comic Con London（October 2026）</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>23–25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>兴趣类(游戏/动漫/流行文化)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>The Gaming Corner</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="7" t="n"/>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MCM Comic Con London（October 2026）</t>
+          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>ExCeL London, 1 Western Gateway, Royal Victoria Dock, London E16 1XL</t>
+          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2704,12 +2703,12 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>23–25 Oct 2026</t>
+          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>兴趣类(游戏/动漫/流行文化)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -2719,22 +2718,22 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>英国最大流行文化展之一，一年两届长期举办；官方已公布 Critical Role 为首批嘉宾</t>
+          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>https://www.mcmcomiccon.com/london/en-us/tickets.html ; https://www.excel.london/whats-on/mcm-comic-con-2026 ; https://www.mcmcomiccon.com/global/en-us/blog/gaming/critical-role-guests-mcm-london-october-2026.html</t>
+          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>游戏、动漫、cosplay 一站式，年轻人浓度高；ExCeL 在东伦敦，QMUL 过去最方便</t>
+          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>The Gaming Corner</t>
+          <t>Reel Talk Club</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
@@ -2754,27 +2753,27 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>BFI London Film Festival 第 70 届（最后几天 + 闭幕）</t>
+          <t>Frieze London &amp; Frieze Masters 2026</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BFI Southbank, Belvedere Road, London SE1 8XT（闭幕式：Royal Festival Hall, Southbank Centre）</t>
+          <t>The Regent's Park, London</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>7–18 Oct 2026（窗口内为 15–18 Oct；闭幕 18 Oct）</t>
+          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>电影/媒体</t>
+          <t>兴趣类(艺术/展览)</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -2784,22 +2783,22 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>第 70 届，英国最重要的电影节之一；闭幕片 The Debut（Jesse Eisenberg）英国首映</t>
+          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>https://whatson.bfi.org.uk/lff/Online/default.asp ; https://en.wikipedia.org/wiki/2026_BFI_London_Film_Festival</t>
+          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>大量首映场，有不少普通票价场次；KCL 就在隔壁。窗口只覆盖最后 4 天，要推得早</t>
+          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Reel Talk Club</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
@@ -2819,27 +2818,27 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Frieze London &amp; Frieze Masters 2026</t>
+          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>15–18 Oct 2026（公众开放；14 Oct 仅限邀请）</t>
+          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>兴趣类(艺术/展览)</t>
+          <t>年轻人娱乐(烟花/音乐节)</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -2849,17 +2848,17 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>国际一线艺术博览会，每年固定在 Regent's Park 举办</t>
+          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>https://www.frieze.com/fairs/frieze-london-frieze-masters/visitor-information ; https://www.royalparks.org.uk/events/frieze-london-frieze-masters</t>
+          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>艺术生必去；⚠️票价偏高，只能网上买、不能再次入场，推之前查一下有没有学生票</t>
+          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -2884,12 +2883,12 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace Fireworks &amp; Drone Festival</t>
+          <t>Battersea Park Fireworks 2026</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
+          <t>Battersea Park, London SW11 4NJ</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2899,12 +2898,12 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:00 烟花）/ 8 Nov 2026（周日，18:00 烟花）</t>
+          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐节)</t>
+          <t>年轻人娱乐(烟花/音乐)</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -2914,22 +2913,22 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>伦敦最大的篝火夜活动之一，年年办；Time Out 有专文；周六由 Eats Everything 做 DJ 压轴</t>
+          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>https://www.alexandrapalace.com/whats-on/fireworks-drone-festival/ ; https://www.timeout.com/london/news/alexandra-palace-fireworks-drone-show-2026-details-revealed-091026</t>
+          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>从 £10.50（早鸟）/ £18 起；周六是成人派对氛围（DJ + 德国啤酒节），适合学生</t>
+          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Live Music Crew</t>
+          <t>St Mary's University, Twickenham</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
@@ -2949,27 +2948,27 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park Fireworks 2026</t>
+          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Battersea Park, London SW11 4NJ</t>
+          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>7 Nov（周六，20:30 烟花）/ 8 Nov 2026（周日，19:00 烟花）</t>
+          <t>14 Nov 2026（周六）11:00–15:30</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/音乐)</t>
+          <t>本地生活类(城市传统活动)</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -2979,22 +2978,22 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>Wandsworth Council 主办，年年举办；当地媒体称预计再次售罄；周六 Rudimental DJ set</t>
+          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>https://www.batterseaparkfireworks.com/ ; https://www.london-now.co.uk/news/26529624.battersea-park-fireworks-2026-tickets-sale-week/</t>
+          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>RCA Battersea 校区就在旁边；有 happy hour（游乐设施半价、饮品 £5），学生友好</t>
+          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>Live Music Crew；St Mary's University, Twickenham</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
@@ -3014,27 +3013,27 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Lord Mayor's Show 2026（伦敦金融城市长巡游）</t>
+          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>14 Nov 2026（周六）11:00–15:30</t>
+          <t>31 Oct 2026（周六）18:30</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>本地生活类(城市传统活动)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -3044,22 +3043,22 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>数百年历史的年度巡游，官方确认 2026 年日期</t>
+          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>https://www.lordmayorsshow.london/ ; https://londonist.com/london/things-to-do/a-guide-to-the-lord-mayor-s-show</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>免费、在市中心，留学生能体验很"英国"的传统活动；LSE/KCL 走路就到</t>
+          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
@@ -3074,82 +3073,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Skindred 万圣节专场（嘉宾：Alien Ant Farm / Spineshank / Orgy）</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Alexandra Palace, Alexandra Palace Way, London N22 7AY</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>31 Oct 2026（周六）18:30</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>年轻人娱乐(Live Music/摇滚)</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>NME、Kerrang! 专门报道的巡演压轴场；在 See Tickets 正规售票；四支乐队同台</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/alexandra-palace/3619860 ; https://www.nme.com/news/music/skindred-announce-2026-uk-and-ireland-tour-with-alien-ant-farm-including-halloween-alexandra-palace-gig-3936573</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>万圣节夜的 nu-metal 怀旧大场，Ally Pally 场馆有气势</t>
-        </is>
-      </c>
-      <c r="M37" s="8" t="inlineStr">
-        <is>
-          <t>Live Music Crew</t>
-        </is>
-      </c>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>University of St Andrews</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>待制作：University of St Andrews.png</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: ST ANDREWS 👇
@@ -3159,14 +3093,79 @@
 🎞️ Byre Thursday Films, St Andrews — easy study-break screenings, 29 Oct / 5 &amp; 12 Nov.</t>
         </is>
       </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Alan Carr 单口喜剧巡演 @ Byre Theatre</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>20 Oct 2026（周二）</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>知名喜剧人巡演场；Byre 是 St Andrews 大学主办的剧院，官方活动日历有列出；小剧场，座位少</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>https://byretheatre.com/upcoming/ ; https://events.st-andrews.ac.uk/event-location/byre/</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>在小镇能看到一线喜剧人很难得，就在校园边上；座位有限，要早买</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="7" t="n"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Alan Carr 单口喜剧巡演 @ Byre Theatre</t>
+          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
+          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -3176,12 +3175,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>20 Oct 2026（周二）</t>
+          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(喜剧)</t>
+          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -3191,22 +3190,22 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>知名喜剧人巡演场；Byre 是 St Andrews 大学主办的剧院，官方活动日历有列出；小剧场，座位少</t>
+          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>https://byretheatre.com/upcoming/ ; https://events.st-andrews.ac.uk/event-location/byre/</t>
+          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>在小镇能看到一线喜剧人很难得，就在校园边上；座位有限，要早买</t>
+          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Day Trip Buddies；University of Stirling</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
@@ -3226,12 +3225,12 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Knockhill Live-Action &amp; Fireworks Spectacular（赛车表演 + 篝火烟花）</t>
+          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Knockhill Racing Circuit, Dunfermline, Fife KY12 9TF</t>
+          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3241,37 +3240,37 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>7 Nov 2026（周六）13:00 开门，14:00 赛道表演，约 17:30 放烟花</t>
+          <t>23 Oct 2026（周五）</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(烟花/赛车) + 一日游</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>中热度</t>
+          <t>年轻人娱乐(喜剧)</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>潜在价值</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>苏格兰国家赛车场官方主办，年年举办；烟花由 Edinburgh 21CC Fireworks 制作；What's On Fife 收录</t>
+          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>https://www.knockhill.com/events/fixture-Live-Action-amp-Fireworks-Spectacular-id917 ; https://www.whatsonfife.co.uk/event/078801-live-action-and-fireworks-spectacular-at-knockhill</t>
+          <t>https://byretheatre.com/upcoming/</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>赛车漂移表演 + 烟花，很特别；离 Stirling 约 35 公里、离 St Andrews 约 50 公里，适合组团开车去</t>
+          <t>周五晚上的喜剧场，就在校园边上</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>Day Trip Buddies；University of Stirling</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
@@ -3291,7 +3290,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Rich Hall 单口喜剧 @ Byre Theatre</t>
+          <t>Byre Theatre 周四电影放映</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3306,12 +3305,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>23 Oct 2026（周五）</t>
+          <t>29 Oct / 5 Nov / 12 Nov 2026（都是周四）</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(喜剧)</t>
+          <t>电影/媒体</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -3321,17 +3320,17 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Byre Theatre 官方节目单有列出；没有售票数据</t>
+          <t>大学剧院固定的放映场，官方节目单有列出</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>https://byretheatre.com/upcoming/</t>
+          <t>https://byretheatre.com/upcoming/film/</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>周五晚上的喜剧场，就在校园边上</t>
+          <t>便宜又方便的学习间隙放松，片单看官网</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
@@ -3351,138 +3350,139 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Byre Theatre 周四电影放映</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>The Byre Theatre, Abbey Street, St Andrews KY16 9LA</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>29 Oct / 5 Nov / 12 Nov 2026（都是周四）</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>电影/媒体</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>潜在价值</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>大学剧院固定的放映场，官方节目单有列出</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>https://byretheatre.com/upcoming/film/</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>便宜又方便的学习间隙放松，片单看官网</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>待制作：Glasgow City College.png</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: GLASGOW NIGHTS 👇
 🧟 GlasGLOW: Zombie Zoo, Glasgow Botanic Gardens — Glasgow's biggest Halloween light trail, late Oct–1 Nov.
-🤘 Core. Festival, Glasgow — heavy music weekend incl. Skindred at the Barrowland, 13–15 Nov.
+🤘 Core. Festival, Glasgow — a heavy-music weekend with Pig Destroyer, Eyehategod &amp; more, 13–15 Nov.
+🎸 Skindred, Barrowland Ballroom, Glasgow — the "You Got This" tour hits a legendary venue, 13 Nov.
 🎸 Pop Mutations x Tiny Changes, Glasgow — an indie weekender across four grassroots venues, 13–14 Nov.</t>
         </is>
       </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>年轻人娱乐(沉浸式/万圣节)</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>高热度</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>University of West of Scotland</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>未取图：云端环境出站被拦（WebFetch EGRESS_BLOCKED），需在本地 Claude Code 补</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="7" t="n"/>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>itison GlasGLOW 2026：Zombie Zoo 万圣节灯光夜游</t>
+          <t>Core. 重型音乐节（Pig Destroyer / Eyehategod / Wormrot / Raging Speedhorn 等）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Glasgow Botanic Gardens, 730 Great Western Road, Glasgow G12 0UE</t>
+          <t>Glasgow 多个场地（具体场地看官网和 What's On Glasgow）</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>city_only</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>⚠️起始日两种说法：16 Oct 或 24 Oct 开始，1–2 Nov 结束（24 Oct–1 Nov 两种说法都覆盖）</t>
+          <t>13–15 Nov 2026</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(沉浸式/万圣节)</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>高热度</t>
+          <t>年轻人娱乐(Live Music/金属)</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>中热度</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>第 8 年举办；自称英国最大的万圣节活动；往年曾因需求大加售数千张票（Scottish Daily Express 报道）</t>
+          <t>What's On Glasgow 收录，号称"苏格兰最新的重型音乐节"，今年第二届；阵容里有 Pig Destroyer、Eyehategod 等国际乐队</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>https://www.itison.com/glasglow ; https://www.glasgowworld.com/news/glasglow-botanic-gardens-dates-5290284 ; https://www.scottishdailyexpress.co.uk/news/scottish-news/glasglow-botanic-gardens-thousands-extra-30877210</t>
+          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://corepresents.seetickets.com/search/all</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>格拉斯哥万圣节季最火的项目，60 分钟沉浸式僵尸主题路线；要分时段买票，热门时段会卖完</t>
+          <t>金属、硬核爱好者的周末；多个场馆可以串场</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>University of West of Scotland</t>
+          <t>Live Music Crew</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
@@ -3502,27 +3502,27 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Core. 重型音乐节（含 Skindred @ Barrowland）</t>
+          <t>Skindred "You Got This" 巡演 格拉斯哥站</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT（Skindred 场）；其余场次分布在格拉斯哥多个场地</t>
+          <t>Barrowland Ballroom, 244 Gallowgate, Glasgow G4 0TT</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>13–15 Nov 2026（Skindred：13 Nov 周五 19:00 开门）</t>
+          <t>13 Nov 2026（周五）19:00 开门</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>年轻人娱乐(Live Music/金属)</t>
+          <t>年轻人娱乐(Live Music/摇滚)</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>What's On Glasgow 收录的"苏格兰最新重型音乐节"，今年第二届；Skindred 是正在英国巡演的成熟乐队，Barrowland 场有独立票务页</t>
+          <t>全英巡演的格拉斯哥站，Visit Glasgow 有收录；和 Core. 音乐节同一个周末，但不属于 Core. 阵容</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>https://www.whatsonglasgow.co.uk/event/118210-core./ ; https://www.visitglasgow.com/events/skindred-13112026-139289</t>
+          <t>https://www.visitglasgow.com/events/skindred-13112026-139289 ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>金属、摇滚爱好者的周末；Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
+          <t>Barrowland 是格拉斯哥的传奇场馆；14 岁以上可入场</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>NME、Kerrang! 报道的全英巡演；成熟乐队，有官方巡演日程</t>
+          <t>NME、Kerrang! 报道的全英巡演；See Tickets、Live Nation 正规售票；嘉宾 Alien Ant Farm、Spineshank</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>https://www.hitthelights.co.uk/tour-news/2026/skindred-uk-tour-dates/ ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
+          <t>https://www.seetickets.com/event/skindred-you-got-this-tour/o2-academy-birmingham/3619857 ; https://www.kerrang.com/skindred-2026-uk-ireland-headline-tour-london-alexandra-palace-alien-ant-farm-spineshank-nu-metal</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>Live Music Crew；UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
+          <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>新办的爵士节（Visit County Durham 报道"新创办"），UK Jazz News 有收录；还没有售票数据</t>
+          <t>2025 年创办，今年第二届；UK Jazz News、Visit County Durham 都有报道；还没有售票数据</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
@@ -6609,7 +6609,7 @@
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: CARDIFF 👇
 ⛸️ Cardiff's Winter Wonderland, Cardiff Castle — ice skating in a castle, from 12 Nov.
-🔥 St Fagans Halloween Nights, Cardiff — Welsh folklore and a Wicker Man burning each night, 29–31 Oct.
+🔥 St Fagans Halloween Nights, Cardiff — Welsh folklore and a Wicker Man burning each night, £16, 29–31 Oct.
 🏉 Wales v Japan, Principality Stadium — Nations Championship rugby, 7 Nov.
 🏉 Wales v New Zealand, Principality Stadium — the big one against the All Blacks, 14 Nov.
 🎄 Cardiff Christmas Market, Cardiff city centre — plus a new Victorian market on Queen St (12–15 Nov), from 12 Nov.
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
-          <t>威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
+          <t>票价 £16；威尔士民俗 + 万圣节，还有鬼屋 disco 和游乐场；必须提前买票</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr">
@@ -7217,79 +7217,79 @@
   <autoFilter ref="A1:O95"/>
   <mergeCells count="75">
     <mergeCell ref="B53:B55"/>
-    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="B27:B28"/>
     <mergeCell ref="A57:A59"/>
-    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="C73:C76"/>
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B2:B3"/>
     <mergeCell ref="C45:C46"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A67:A72"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B10:B18"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="A79:A81"/>
     <mergeCell ref="A93:A95"/>
     <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A27:A28"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="A87:A92"/>
     <mergeCell ref="B73:B76"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A41:A44"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B47:B49"/>
-    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="C10:C17"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A10:A18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B67:B72"/>
+    <mergeCell ref="B30:B36"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B93:B95"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B67:B72"/>
     <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="A73:A76"/>
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C27:C28"/>
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B37:B40"/>
     <mergeCell ref="B87:B92"/>
-    <mergeCell ref="A31:A37"/>
     <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A50:A52"/>
     <mergeCell ref="C79:C81"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B31:B37"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="C50:C52"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C30:C36"/>
+    <mergeCell ref="B41:B44"/>
     <mergeCell ref="C67:C72"/>
     <mergeCell ref="C93:C95"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B21:B25"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="C20:C24"/>
     <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C28:C29"/>
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="C77:C78"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="C87:C92"/>
+    <mergeCell ref="C37:C40"/>
     <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="C10:C18"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7673,11 +7673,11 @@
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>都来自城市轮顺带（烟花节 DJ、Skindred 巡演、格拉斯哥音乐节）；还没专门做全国演出轮</t>
+          <t>都来自城市轮顺带（巡演、音乐节、club 活动）；烟花节虽有 DJ，但不算演出，没放进这个群</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9350,17 +9350,53 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
+          <t>已更正</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Core. 音乐节：之前写成"含 Skindred"，其实 Skindred 格拉斯哥站（11/13 Barrowland）是独立巡演，现在拆成两条</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>已更正</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Durham Jazz Festival：之前写"新办"，实际 2025 年创办，今年第二届</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>已更正</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Live Music Crew：去掉了 Ally Pally、Battersea 两个烟花节（有 DJ 但主体是烟花，和 Valorant 群推 CS 内容是同一类错误）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B26"/>
+  <autoFilter ref="A1:B29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Track B 30天活动'!$A$1:$O$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'社群覆盖清单'!$A$1:$E$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核实与缺口'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核实与缺口'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,12 +632,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Kettering Leisure Village, Kettering, Northamptonshire</t>
+          <t>Arena Sports, Kettering Leisure Village, Thurston Drive, Kettering NN15 6PB</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Kettering Leisure Village, Kettering, Northamptonshire</t>
+          <t>Arena Sports, Kettering Leisure Village, Thurston Drive, Kettering NN15 6PB</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal TF11 8LE</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -991,7 +991,7 @@
           <t>🔍 Event Radar (UK) — what's worth doing this month.
 This month: GIRLS' NIGHTS OUT 👇
 🔮 The Craft 30th Anniversary Screening, Salford — an immersive witchy Halloween movie night by Girl Gang, 31 Oct.
-🧹 Season of the Witch, Manchester — Girl Gang's craft nights &amp; witchy events, 4 Oct–22 Nov.
+🧹 Season of the Witch, Manchester — Girl Gang's craft nights &amp; witchy events, to 22 Nov.
 💬 Lonely Girls Club Meet-up, Manchester — a solo-friendly night to make new friends, £8.95, 27 Oct.</t>
         </is>
       </c>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Islington Mill, James Street, Salford M3 5HW</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1067,17 +1067,17 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Manchester 多个场地：Craft &amp; Coven 手工夜在 Cloudwater Taproom；其余场次（含 Pendle 徒步）场地和日期要看 girlgangmcr.com</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>22 Sep – 22 Nov 2026（窗口内为 15 Oct – 15 Nov；单场日期见官网）</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Manchester（⚠️具体场地报名后才公布，官网没公开）</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Glasgow 多个场地（具体场地看官网和 What's On Glasgow）</t>
+          <t>Glasgow 多个场地：The Art School（20 Scott Street）、Nice N Sleazy（421 Sauchiehall Street）、Garnethill Multicultural Centre、Woodside Hall（11/15 Pig Destroyer 场）</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Glasgow 4 家场馆：The Old Hairdressers（Renfield Lane）、Stereo（Renfield Lane）、Mono（King's Court）、The Glad Café（Pollokshaws Road）</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>Sheffield 多个场地：Montgomery Theatre（27 Surrey Street）、Lyceum Theatre、Firth Hall（University of Sheffield）、Millennium Gallery 等</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Islington Mill, James Street, Salford M3 5HW</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Cardiff（多个场地）</t>
+          <t>Cineworld Cardiff, Mary Ann Street, Cardiff CF10 2EN（主场馆）</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, 1 Summerhall, Edinburgh EH9 1PL</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Capernwray Diving Centre, Jackdaw Quarry, Capernwray Road, Over Kellet, Carnforth LA6 1AD</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Kettering Leisure Village, Kettering, Northamptonshire</t>
+          <t>Arena Sports, Kettering Leisure Village, Thurston Drive, Kettering NN15 6PB</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>The Regent's Park, London</t>
+          <t>The Regent's Park, London NW1（Frieze London 和 Frieze Masters 两个帐篷都在园内，入口以官网为准）</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>City of London，从 Mansion House 出发（全程约 3 英里）</t>
+          <t>City of London：Mansion House 出发 → Royal Courts of Justice（Strand）→ 返回，沿途都能看</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Glasgow 多个场地（具体场地看官网和 What's On Glasgow）</t>
+          <t>Glasgow 多个场地：The Art School（20 Scott Street）、Nice N Sleazy（421 Sauchiehall Street）、Garnethill Multicultural Centre、Woodside Hall（11/15 Pig Destroyer 场）</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>The Old Hairdressers / Mono / The Glad Café / Stereo（格拉斯哥 4 家独立场馆）</t>
+          <t>Glasgow 4 家场馆：The Old Hairdressers（Renfield Lane）、Stereo（Renfield Lane）、Mono（King's Court）、The Glad Café（Pollokshaws Road）</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Paisley town centre（游行路线经过 Mill Street）</t>
+          <t>Paisley town centre：游行走 Smithhills St → Gauze St → Mill St → Bridge St → Cotton St → St Mirren Brae → Causeyside St → Orchard St；街头表演在 County Square，舞台在 Bridge Street 停车场</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Edinburgh（多个场地）</t>
+          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, 1 Summerhall, Edinburgh EH9 1PL</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Briarlands Farm, Stirling（Cambusbarron / Craigforth 一带，具体地址见官网）</t>
+          <t>Briarlands Farm, Blairdrummond, Stirling FK9 4UP</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Weston Park, Weston-under-Lizard, Shifnal, Shropshire</t>
+          <t>Weston Park, Weston-under-Lizard, Shifnal TF11 8LE</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Sheffield（市内多个场地）</t>
+          <t>Sheffield 多个场地：Montgomery Theatre（27 Surrey Street）、Lyceum Theatre、Firth Hall（University of Sheffield）、Millennium Gallery 等</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Lancaster city centre（历史建筑和街区）</t>
+          <t>Lancaster city centre：Market Square、Dalton Square、The Storey Gardens、Lancaster Castle、Quay Meadow 等（完整地图见 lightuplancaster.co.uk）</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Capernwray Dive Centre, Capernwray, Carnforth, Lancashire</t>
+          <t>Capernwray Diving Centre, Jackdaw Quarry, Capernwray Road, Over Kellet, Carnforth LA6 1AD</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -5214,7 +5214,7 @@
 🎆 Free Council Fireworks, Platt Fields, Fallowfield — lantern parade + fireworks, completely free, 7 Nov.
 🎧 The Warehouse Project Halloween: NeXup, Depot Mayfield — house &amp; tech house till 4am (18+), 31 Oct.
 🔮 The Craft 30th Anniversary Screening, Salford — an immersive witchy Halloween movie night by Girl Gang, 31 Oct.
-🧹 Season of the Witch, Manchester — Girl Gang's craft nights &amp; witchy events, 4 Oct–22 Nov.
+🧹 Season of the Witch, Manchester — Girl Gang's craft nights &amp; witchy events, to 22 Nov.
 💬 Lonely Girls Club Meet-up, Manchester — a solo-friendly night to make new friends, £8.95, 27 Oct.</t>
         </is>
       </c>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Islington Mill, James Street, Salford</t>
+          <t>Islington Mill, James Street, Salford M3 5HW</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Manchester 多个场地</t>
+          <t>Manchester 多个场地：Craft &amp; Coven 手工夜在 Cloudwater Taproom；其余场次（含 Pendle 徒步）场地和日期要看 girlgangmcr.com</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>4 Oct – 22 Nov 2026（单场日期见官网）</t>
+          <t>22 Sep – 22 Nov 2026（窗口内为 15 Oct – 15 Nov；单场日期见官网）</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Manchester（场地待公布）</t>
+          <t>Manchester（⚠️具体场地报名后才公布，官网没公开）</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Beamish Museum, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Beamish Museum, Regional Museums Store, Beamish, County Durham DH9 0RG</t>
+          <t>Beamish Museum, Beamish, County Durham DH9 0RG</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Gala Theatre / Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms 等，Durham</t>
+          <t>Gala Theatre &amp; Gala Studio（Millennium Place, Durham）/ Redhills (Durham Miners' Hall) / Sir Thomas Allen Assembly Rooms / Old Cinema Launderette（Gilesgate）等</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -6053,17 +6053,17 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Leeds city centre（40 多处装置，Briggate 等）</t>
+          <t>Leeds city centre：信息点在 Millennium Square；主要区域有 Briggate、Town Hall、Corn Exchange、Civic Hall、South Bank（Royal Armouries 一带）</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>venue_only</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>28–29 Oct 2026（周三、周四）18:00–21:30</t>
+          <t>28–29 Oct 2026（周三、周四）18:00 起（结束时间有 21:30 和 22:00 两种说法）</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>DRAM Centre, Dalton, Huddersfield（与 Moldgreen ARLFC 合办）</t>
+          <t>DRAM Sport &amp; Community Centre, Ridgeway, Dalton, Huddersfield HD5 9QJ</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Mirfield Showground, Mirfield, West Yorkshire</t>
+          <t>Mirfield Showground, Huddersfield Road, Mirfield WF14 9NE</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>venue_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent City Centre（Hanley）</t>
+          <t>Hanley city centre, Stoke-on-Trent（City Centre BID 主办；⚠️具体街区官方没写）</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>31 Oct 2026（周六）10:00 起</t>
+          <t>31 Oct 2026（周六）10:00 起（Facebook 活动页写的日期）</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Cardiff（多个场地）</t>
+          <t>Cineworld Cardiff, Mary Ann Street, Cardiff CF10 2EN（主场馆）</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>city_only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>The Lemon Tree / Cowdray Hall / King's Pavilion 等，Aberdeen &amp; Aberdeenshire</t>
+          <t>Aberdeen &amp; Aberdeenshire 多个场地：The Lemon Tree（5 West North Street, AB24 5AT）、Cowdray Hall、King's Pavilion、Aberdeen Art Gallery、Maritime Museum、Anatomy Rooms，另有一场在前核掩体</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Aberdeen Beach / Beach Boulevard 一带（往年因海滩施工改在 North Pier 燃放）</t>
+          <t>Aberdeen Beach Esplanade 南段观看；往年烟花从 Port of Aberdeen North Pier 尽头燃放（⚠️2026 年的安排还没公布）</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -9040,7 +9040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9386,17 +9386,53 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
+          <t>已更正</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Briarlands Farm：之前写"Cambusbarron / Craigforth 一带"是猜的，实际在 Blairdrummond, FK9 4UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>已更正</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Girl Gang Season of the Witch：整季其实从 22 Sep 开始，不是 4 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>地址未明</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Lonely Girls Club 10/27：场地报名后才公布；Stoke 万圣节街头派对：只知道在 Hanley 市中心；Aberdeen 烟花：2026 年燃放点还没公布</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
           <t>窗口提醒</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>BFI 伦敦电影节只有 15–18 Oct 在窗口内；Frieze 在 15–18 Oct，要推得早</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B29"/>
+  <autoFilter ref="A1:B32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>The Gaming Corner</t>
@@ -686,7 +686,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="7" t="n"/>
@@ -751,7 +751,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CS2 Frag Hub</t>
@@ -830,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Day Trip Buddies</t>
@@ -910,7 +910,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -975,7 +975,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Girls' Corner</t>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="7" t="n"/>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="85" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Live Music Crew</t>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="58" customHeight="1">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="71.5" customHeight="1">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="71.5" customHeight="1">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="58" customHeight="1">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="71.5" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="71.5" customHeight="1">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="58" customHeight="1">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="71.5" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Page Turners Club</t>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="58" customHeight="1">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="71.5" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Reel Talk Club</t>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="71.5" customHeight="1">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="58" customHeight="1">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="58" customHeight="1">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="58" customHeight="1">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="71.5" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Snack Finds &amp; Picks</t>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="73.5" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Swim Wave Tribe</t>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="71.5" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>UK Food Lovers</t>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="71.5" customHeight="1">
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Valorant Riot Crew</t>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="71.5" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>UCL Hub / IC Collective / Royal College of Art / King's College London / London School of Economics / Queen Mary University of London</t>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="58" customHeight="1">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="7" t="n"/>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="58" customHeight="1">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="58" customHeight="1">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="7" t="n"/>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="58" customHeight="1">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="7" t="n"/>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="58" customHeight="1">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="85" customHeight="1">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>University of St Andrews</t>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="71.5" customHeight="1">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="7" t="n"/>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="71.5" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Glasgow City College / Glasgow Caledonian University / University of Strathclyde</t>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="71.5" customHeight="1">
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="71.5" customHeight="1">
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="7" t="n"/>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="58" customHeight="1">
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="7" t="n"/>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="71.5" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>University of West of Scotland</t>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="71.5" customHeight="1">
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="7" t="n"/>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="58" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Heriot-Watt University / University of Edinburgh Freshers 2026</t>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="71.5" customHeight="1">
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="7" t="n"/>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="58" customHeight="1">
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="7" t="n"/>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="71.5" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>University of Stirling</t>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="58" customHeight="1">
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="7" t="n"/>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="58" customHeight="1">
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="7" t="n"/>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="71.5" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>BCU Fresher Hub 2026 / Aston Fresher Hub 2026 / SCCB| Birmingham Student Life</t>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="58" customHeight="1">
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="7" t="n"/>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="71.5" customHeight="1">
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="7" t="n"/>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Wolverhampton Freshers Hub 2026 / Harper Adams Campus Life</t>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="58" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Sheffield Hallam University / University of Sheffield</t>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="58" customHeight="1">
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="7" t="n"/>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="58" customHeight="1">
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="7" t="n"/>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="71.5" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>St Mary's University, Twickenham</t>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="58" customHeight="1">
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="7" t="n"/>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="58" customHeight="1">
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="7" t="n"/>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="58" customHeight="1">
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="7" t="n"/>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="71.5" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>University of Lancaster</t>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="58" customHeight="1">
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n"/>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="73.5" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>University of Chester</t>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="71.5" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="58" customHeight="1">
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="7" t="n"/>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="58" customHeight="1">
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="7" t="n"/>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="58" customHeight="1">
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="7" t="n"/>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="58" customHeight="1">
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="7" t="n"/>
@@ -5539,7 +5539,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="58" customHeight="1">
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="7" t="n"/>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="58" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Newcastle university / Newcastle university 2 / Northumbria university</t>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="58" customHeight="1">
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="7" t="n"/>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="58" customHeight="1">
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="7" t="n"/>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="71.5" customHeight="1">
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="7" t="n"/>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="58" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Durham university</t>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="71.5" customHeight="1">
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="7" t="n"/>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="85" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Leeds Uni Student Hub / Leeds University group 2</t>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="71.5" customHeight="1">
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="7" t="n"/>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="58" customHeight="1">
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="7" t="n"/>
@@ -6237,7 +6237,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="58" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Huddersfield Uni Student Hub</t>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="58" customHeight="1">
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="7" t="n"/>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="58" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Staffs Student Life | Stoke / Keele Campus Life</t>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="58" customHeight="1">
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="6" t="n"/>
       <c r="C85" s="7" t="n"/>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="58" customHeight="1">
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="7" t="n"/>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="58" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>University of Cardiff / Cardiff Metropolitan University</t>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="58" customHeight="1">
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="7" t="n"/>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="71.5" customHeight="1">
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="7" t="n"/>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="58" customHeight="1">
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="6" t="n"/>
       <c r="C90" s="7" t="n"/>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="58" customHeight="1">
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="7" t="n"/>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="58" customHeight="1">
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="7" t="n"/>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="71.5" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>University of Aberdeen Freshers 2026</t>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="71.5" customHeight="1">
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="7" t="n"/>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="58" customHeight="1">
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="7" t="n"/>

--- a/data/UK_Events_TrackB_10.15-11.15.xlsx
+++ b/data/UK_Events_TrackB_10.15-11.15.xlsx
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, 1 Summerhall, Edinburgh EH9 1PL</t>
+          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, Edinburgh</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, 1 Summerhall, Edinburgh EH9 1PL</t>
+          <t>Filmhouse, 88 Lothian Road, Edinburgh EH3 9BZ / Summerhall, Edinburgh</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
